--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT51"/>
+  <dimension ref="A1:AT56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2282,11 +2282,7 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>[registration status] SEC IAPD registration (CRD 329017) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via an independently verified firm website. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
-        </is>
-      </c>
+      <c r="AT13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4224,7 +4220,7 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -4232,11 +4228,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
@@ -4270,11 +4262,7 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone; estimated_aum; website; investment_thesis; principal_name; principal_title</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>CORRECTION (2026-07-28): the firm's generic name had caused an unrelated company's website (thefamilyoffice.com, a residential real-estate advisory) to be attached; all website-derived fields were removed. Retained facts are IAPD-verified only (name, Redmond WA location, family-office registration). SEC registration confirmed inactive/withdrawn (IAPD firm search, 2026-07-28).</t>
-        </is>
-      </c>
+      <c r="AT27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6282,11 +6270,7 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT41" t="inlineStr">
-        <is>
-          <t>[registration status] SEC IAPD registration (CRD 158123) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via an independently verified firm website. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
-        </is>
-      </c>
+      <c r="AT41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7030,11 +7014,7 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT46" t="inlineStr">
-        <is>
-          <t>[registration status] SEC IAPD registration (CRD 307858) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via a recent SEC Form 13F filing (period 2024-09-30). (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
-        </is>
-      </c>
+      <c r="AT46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7330,11 +7310,7 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT48" t="inlineStr">
-        <is>
-          <t>[registration status] SEC IAPD registration (CRD 134062) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via SEC Form ADV Item 5.F regulatory AUM and Form 13F filings. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
-        </is>
-      </c>
+      <c r="AT48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7672,6 +7648,626 @@
       </c>
       <c r="AT51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Financière Agache</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Le groupe familial Arnault détenant au total 97,5% de Christian Dior". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Holding company of the Arnault family, controlling shareholder of Christian Dior.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Florian Ollivier</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Président-directeur général</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>KIRKBI</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "As the holding company of the Kirk Kristiansen family, who founded the LEGO Group in 1932". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Holding and investment company of the Kirk Kristiansen family, founders of the LEGO Group; owns and develops businesses for the long term.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Billund</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone; principal_name; principal_title</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Controlled by the Kirk Kristiansen family; no individual decision-maker is named on the site, so the principal is left could_not_verify. The firm also appears in SEC EDGAR full-text filings (Schedule 13D/13G on US holdings), corroborating its investing activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Prime Opportunities Investment Group</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "our background as a successful family office with extensive real estate holdings and business operating experience". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>US single-family office investing in public equities with a private-equity approach; roots in real-estate holdings and operating businesses.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>We invest only in publicly traded companies, and take a private equity approach to our investment process.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Pouya David Yadegar</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Founder, Chief Investment Officer</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Self-describes as a single-family office; a smaller, public-equity focused firm — held at Low confidence pending a second authoritative source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Korys</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Korys is the entrepreneurial investment company of the Colruyt family.". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Entrepreneurial investment company of the Colruyt family, investing in companies aligned with conscious-consumer solutions.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Korys invests in companies that offer solutions to the challenges conscious consumers face in their search for products and services.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone; principal_name; principal_title</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Controlled by the Colruyt family; no individual decision-maker is named on the site, so the principal is left could_not_verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Builders Vision</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Lukas Walton founded Builders Vision in 2018, inspired by the belief that philanthropy and investing together can shift capital markets toward sustainable solutions.". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Impact platform founded by Lukas Walton in 2018 that combines philanthropy and investing to shift capital markets toward sustainable solutions.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Lukas Walton</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The firm also appears in SEC EDGAR full-text filings on US holdings, corroborating its investing activity.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7683,7 +8279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13260,7 +13856,7 @@
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -13278,7 +13874,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -13294,7 +13890,7 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -13312,7 +13908,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>principal_name</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -13328,7 +13924,7 @@
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -18505,6 +19101,1070 @@
         </is>
       </c>
       <c r="H318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>principal_name</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>principal_title</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>principal_name</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>principal_title</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>principal_name</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>principal_title</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18517,7 +20177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22631,6 +24291,286 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>family-office status, type, firm identity</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>family-office status, type, firm identity</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>family-office status, type, firm identity</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>family-office status, type, firm identity</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>family-office status, type, firm identity</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -665,12 +665,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 307144). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Multi-Family Office</t>
+          <t>Undetermined</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>firm website describes itself as a family office; type: single vs multi family not established | firm website: "Wir betreuen nicht nur einzelne Mandanten, sondern häufig auch die gesamte Familie in unserer generationenübergreifenden Betrachtung"</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 167174). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 294025). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 106079). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established | firm website: "At Collective Family Office, we serve as your family’s steward—aligning every part of your balance sheet under one clear, cohesive plan."</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 301274). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 144811). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 107141). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 317615). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration names it a family office; single vs multi family not established from an authoritative on-site statement.</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 110990). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr"/>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration (CRD 288530) registers the entity as a family-office adviser (registered names include 'THE FAMILY OFFICE, LLC' and 'OUR FAMILY OFFICE, LLC'); single- vs multi-family type not established from authoritative sources. SEC registration is currently inactive/withdrawn.</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established | firm website: "A partnership of entrepreneurs serving entrepreneurial families, Callan Family Office’s 23 partners have decades of experience working exclusively with ultra-hi"</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 317446). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established | firm website: "Investment, Family and Legacy Solutions for Successful Multi-Generational Families"</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. SEC Form ADV Item 5.F reports regulatory (client) AUM ($138M total regulatory AUM (SEC Form ADV Item 5.F as of 2023)); a registered adviser managing external client assets is a multi-family office.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 312005). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established | firm website: "Our family office approach supports clients with multi-generational wealth strategies"</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 338015). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 142856). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established | firm website: "Angeles Investments is driven to be an innovative leader in managing investment programs, globally recognized for our positive impact on our clients and industr"</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 338266). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -5373,12 +5373,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 301865). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established | firm website: "Longwall Family Office is an SEC-registered and independently-owned investment advisory firm"</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. SEC Form ADV Item 5.F reports regulatory (client) AUM ($208M total regulatory AUM (SEC Form ADV Item 5.F as of 2023)); a registered adviser managing external client assets is a multi-family office.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established | firm website: "We serve as our clients’ Chief Financial Officer — providing sophisticated tax, estate, and investment solutions concurrent with timely financial analysis to ad"</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. The firm's own website states it serves multiple families / clients: "We serve as our clients’ Chief Financial Officer — providing sophisticated tax, estate, and investment solutions concurrent with timely financial analysis to address the " -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established | firm website: "Eagle Bay Family Office delivers comprehensive family office and investment advisory services for wealthy families"</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. SEC Form ADV Item 5.F reports regulatory (client) AUM ($887M total regulatory AUM (SEC Form ADV Item 5.F as of 2024)); a registered adviser managing external client assets is a multi-family office.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 323016). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration names it a family office; single vs multi family not established from an authoritative on-site statement.</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -6377,12 +6377,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 337597). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr"/>
@@ -6489,12 +6489,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 298272). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 312154). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -6733,7 +6733,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -6965,12 +6965,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 335128). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>Multi-Family Office</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. SEC Form ADV Item 5.F reports regulatory (client) AUM ($5.01B total regulatory AUM (SEC Form ADV Item 5.F as of 2023)); a registered adviser managing external client assets is a multi-family office.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -7171,7 +7171,11 @@
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1354739&amp;type=13F&amp;dateb=&amp;owner=include&amp;count=40</t>
+        </is>
+      </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
@@ -7185,7 +7189,7 @@
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -7216,7 +7220,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address)</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings / recent portfolio activity)</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -7378,7 +7382,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -7486,7 +7490,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -22931,7 +22935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26926,7 +26930,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -26934,8 +26938,16 @@
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>13F holdings / recent portfolio activity</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1354739&amp;type=13F&amp;dateb=&amp;owner=include&amp;count=40</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -26945,29 +26957,21 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>fo_1e72fff8ee</t>
+          <t>fo_519c4712e1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>family-office registration, firm identity &amp; office address</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/155003</t>
-        </is>
-      </c>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -26987,17 +26991,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>13F holdings, aggregate 13(f) value, signatory</t>
+          <t>family-office registration, firm identity &amp; office address</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1538112&amp;type=13F&amp;dateb=&amp;owner=include&amp;count=40</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/155003</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -27019,17 +27023,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>family-office status/type, description, principal</t>
+          <t>13F holdings, aggregate 13(f) value, signatory</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://www.marcuardfamilyoffice.com/</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1538112&amp;type=13F&amp;dateb=&amp;owner=include&amp;count=40</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -27046,16 +27050,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://www.marcuardfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27065,12 +27077,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>fo_38a12a7ca6</t>
+          <t>fo_1e72fff8ee</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -27078,16 +27090,8 @@
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>13F holdings, aggregate 13(f) value, signatory</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1511137&amp;type=13F&amp;dateb=&amp;owner=include&amp;count=40</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27102,7 +27106,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -27110,8 +27114,16 @@
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>13F holdings, aggregate 13(f) value, signatory</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1511137&amp;type=13F&amp;dateb=&amp;owner=include&amp;count=40</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27121,12 +27133,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>fo_4f2b68b968</t>
+          <t>fo_38a12a7ca6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -27134,16 +27146,8 @@
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>13F holdings, aggregate 13(f) value, signatory</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1889527&amp;type=13F&amp;dateb=&amp;owner=include&amp;count=40</t>
-        </is>
-      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27158,7 +27162,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -27166,8 +27170,16 @@
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>13F holdings, aggregate 13(f) value, signatory</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=1889527&amp;type=13F&amp;dateb=&amp;owner=include&amp;count=40</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27177,29 +27189,21 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>fo_ca957ee5d5</t>
+          <t>fo_4f2b68b968</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>family-office status/type, description, principal</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>https://www.financiereagache-finance.com/</t>
-        </is>
-      </c>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27214,16 +27218,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Curated directory / reference (Wikipedia, associations)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27233,29 +27245,21 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>fo_d27cc088a3</t>
+          <t>fo_ca957ee5d5</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>family-office status/type, description, principal</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>https://www.kirkbi.com/</t>
-        </is>
-      </c>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27270,16 +27274,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Curated directory / reference (Wikipedia, associations)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27289,29 +27301,21 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>fo_a750611281</t>
+          <t>fo_d27cc088a3</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>family-office status/type, description, principal</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>https://www.primeopp.com/</t>
-        </is>
-      </c>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27326,16 +27330,24 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Curated directory / reference (Wikipedia, associations)</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27345,29 +27357,21 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>fo_3642e17ac1</t>
+          <t>fo_a750611281</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>family-office status/type, description, principal</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>https://www.korys.be/</t>
-        </is>
-      </c>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27382,16 +27386,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Curated directory / reference (Wikipedia, associations)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27401,29 +27413,21 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>fo_e8d9f15c57</t>
+          <t>fo_3642e17ac1</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>family-office status/type, description, principal</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>https://www.buildersvision.com/</t>
-        </is>
-      </c>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -27438,17 +27442,49 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>discovery</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr">
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -27465,7 +27501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28231,6 +28267,582 @@
         </is>
       </c>
       <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>fo_7ef75c02df</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>fo_33a7413d76</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>reclassified to Undetermined under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fo_4dcf965b7e</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fo_9220a272d8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>fo_15eb1b42d3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>fo_a6f6c19fed</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fo_89137929e9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>fo_da95e70bda</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>fo_5d097b8c75</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>fo_7c7a0fc12b</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>fo_29e17a89bc</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>fo_6103057a41</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>fo_1c9723ce52</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>fo_41fc928853</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fo_c7b90e8baa</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fo_40030db7ab</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>fo_87876deee2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>fo_519c4712e1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fo_type</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>reclassified to Multi-Family Office under the uniform evidence rule (explicit quote / ADV Item 5.F / active registration); replaces a contradictory or unestablished prior label</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
@@ -28414,7 +29026,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Decision-maker identity where verified.</t>
+          <t>The person NAMED ON THE AUTHORITATIVE FILING — the SEC Form 13F signatory (frequently a compliance/operations/legal officer, e.g. CCO/COO/GC), the SEC Form ADV Schedule A control person, or a website-named principal. This is the filing signatory, NOT necessarily the lead investment decision-maker (see KnownLimitations).</t>
         </is>
       </c>
     </row>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -794,7 +794,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -885,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -925,7 +929,7 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -940,7 +944,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
+          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection. [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
         </is>
       </c>
     </row>
@@ -962,7 +966,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1037,7 +1041,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1189,7 +1193,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1202,7 +1206,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1293,7 +1301,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1333,7 +1341,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -1348,7 +1356,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
+          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection. [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1378,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1453,7 +1461,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1486,7 +1494,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1597,7 +1605,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -1610,7 +1618,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1736,7 +1748,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
+          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection. [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1889,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -1890,7 +1902,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2020,7 +2036,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
+          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection. [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2169,7 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2166,7 +2182,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2276,7 +2296,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>[registration status] SEC IAPD registration (CRD 329017) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via an independently verified firm website. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
+          <t>[registration status] SEC IAPD registration (CRD 329017) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via an independently verified firm website. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.) [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2318,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -2409,7 +2429,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -2422,7 +2442,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2554,7 +2578,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2574,7 +2602,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -2693,7 +2721,7 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -2706,7 +2734,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2830,7 +2862,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2981,7 +3017,7 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -2994,7 +3030,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website, SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3085,7 +3125,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -3125,7 +3165,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -3138,7 +3178,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3269,7 +3313,7 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -3282,7 +3326,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3369,7 +3417,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3405,7 +3453,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -3418,7 +3466,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3549,7 +3601,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -3562,7 +3614,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3686,7 +3742,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3841,7 +3901,7 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -3854,7 +3914,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website, SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3968,7 +4032,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>Classification corrected Single-Family Office -&gt; Undetermined on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
+          <t>Classification corrected Single-Family Office -&gt; Undetermined on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection. [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
         </is>
       </c>
     </row>
@@ -3990,7 +4054,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -4109,7 +4173,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -4122,7 +4186,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4142,7 +4210,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4232,7 +4300,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>CORRECTION (2026-07-28): the firm's generic name had caused an unrelated company's website (thefamilyoffice.com, a residential real-estate advisory) to be attached; all website-derived fields were removed. Retained facts are IAPD-verified only. SEC registration confirmed inactive/withdrawn (IAPD firm search, 2026-07-28).</t>
+          <t>CORRECTION (2026-07-28): the firm's generic name had caused an unrelated company's website (thefamilyoffice.com, a residential real-estate advisory) to be attached; all website-derived fields were removed. Retained facts are IAPD-verified only. SEC registration confirmed inactive/withdrawn (IAPD firm search, 2026-07-28). [same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4453,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -4398,7 +4466,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website, SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4521,7 +4593,7 @@
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
@@ -4534,7 +4606,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4665,7 +4741,7 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
@@ -4678,7 +4754,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4810,7 +4890,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4949,7 +5033,7 @@
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -4962,7 +5046,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5086,7 +5174,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5106,7 +5198,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -5225,7 +5317,7 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
@@ -5238,7 +5330,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5356,7 +5452,7 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
+          <t>Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection. [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5585,7 @@
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
@@ -5502,7 +5598,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5637,7 +5737,7 @@
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -5650,7 +5750,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5797,7 +5901,7 @@
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
@@ -5810,7 +5914,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website, SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5937,7 +6045,7 @@
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
@@ -5950,7 +6058,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6081,7 +6193,7 @@
       </c>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
@@ -6094,7 +6206,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6114,7 +6230,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -6193,7 +6309,7 @@
       </c>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
@@ -6208,7 +6324,7 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>Classification corrected Single-Family Office -&gt; Undetermined on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection. [registration status] SEC IAPD registration (CRD 158123) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via an independently verified firm website. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
+          <t>Classification corrected Single-Family Office -&gt; Undetermined on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection. [registration status] SEC IAPD registration (CRD 158123) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via an independently verified firm website. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.) [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website).</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6346,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -6349,7 +6465,7 @@
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
@@ -6362,7 +6478,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6474,7 +6594,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6613,7 +6737,7 @@
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
@@ -6626,7 +6750,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website, SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6781,7 +6909,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
@@ -6794,7 +6922,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email</t>
         </is>
       </c>
-      <c r="AT45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website, SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6814,7 +6946,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (registration inactive/withdrawn), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -6933,7 +7065,7 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
@@ -6948,7 +7080,7 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>[registration status] SEC IAPD registration (CRD 307858) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via a recent SEC Form 13F filing (period 2024-09-30). (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
+          <t>[registration status] SEC IAPD registration (CRD 307858) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via a recent SEC Form 13F filing (period 2024-09-30). (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.) [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7213,7 @@
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
@@ -7094,7 +7226,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7240,7 +7376,7 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>[registration status] SEC IAPD registration (CRD 134062) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via SEC Form ADV Item 5.F regulatory AUM and Form 13F filings. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
+          <t>[registration status] SEC IAPD registration (CRD 134062) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via SEC Form ADV Item 5.F regulatory AUM and Form 13F filings. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.) [same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (SEC IAPD / Form ADV (investment-adviser registration)).</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7485,7 @@
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
@@ -7362,7 +7498,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr">
+        <is>
+          <t>[same-source justification] the discovery source class also documents this firm's facts via the underlying filing; INDEPENDENT cross-verification is provided by a different-class source (Firm Website, SEC IAPD / Form ADV (investment-adviser registration)).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7382,7 +7522,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -7457,7 +7597,7 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
@@ -7470,7 +7610,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7490,7 +7634,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -7565,7 +7709,7 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
@@ -7578,7 +7722,11 @@
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited — disclosed, not fabricated.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7838,7 +7986,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Firm website self-identifies as "a successful family office" but does not establish single vs multi family; discovered via Wikipedia/Wikidata and verified as a family office against its own website.</t>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -8330,7 +8478,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8444,7 +8596,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8482,7 +8638,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9128,7 +9288,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9242,7 +9406,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9280,7 +9448,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9318,7 +9490,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9964,7 +10140,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -10002,7 +10182,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -10040,7 +10224,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -10078,7 +10266,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -10116,7 +10308,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -10154,7 +10350,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -10192,7 +10392,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10496,7 +10700,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10610,7 +10818,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10648,7 +10860,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10686,7 +10902,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -11066,7 +11286,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11180,7 +11404,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11218,7 +11446,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -11446,7 +11678,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11484,7 +11720,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11522,7 +11762,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11560,7 +11804,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11598,7 +11846,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11636,7 +11888,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11674,7 +11930,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11978,7 +12238,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12016,7 +12280,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12054,7 +12322,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12092,7 +12364,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12130,7 +12406,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12168,7 +12448,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12206,7 +12490,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12244,7 +12532,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12624,7 +12916,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12776,7 +13072,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12814,7 +13114,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -13270,7 +13574,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13384,7 +13692,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -13422,7 +13734,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -13840,7 +14156,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13954,7 +14274,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13992,7 +14316,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14372,7 +14700,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14524,7 +14856,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -14562,7 +14898,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -14600,7 +14940,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -14828,7 +15172,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -14866,7 +15214,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -14904,7 +15256,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -14942,7 +15298,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14980,7 +15340,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -15018,7 +15382,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -15056,7 +15424,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -15094,7 +15466,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -15398,7 +15774,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -15550,7 +15930,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15588,7 +15972,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -16006,7 +16394,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -16120,7 +16512,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -16158,7 +16554,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -16538,7 +16938,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -16652,7 +17056,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -16690,7 +17098,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16728,7 +17140,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr"/>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -17032,7 +17448,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -17070,7 +17490,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -17108,7 +17532,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -17146,7 +17574,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -17184,7 +17616,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -17222,7 +17658,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17260,7 +17700,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -17298,7 +17742,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -17564,7 +18012,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17678,7 +18130,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr"/>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -17716,7 +18172,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -18210,7 +18670,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr"/>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -18362,7 +18826,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr"/>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -18400,7 +18868,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -18818,7 +19290,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -18932,7 +19408,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr"/>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -18970,7 +19450,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -19198,7 +19682,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -19236,7 +19724,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr"/>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -19274,7 +19766,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr"/>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -19312,7 +19808,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -19350,7 +19850,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr"/>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -19388,7 +19892,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr"/>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -19426,7 +19934,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr"/>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -19464,7 +19976,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr"/>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -19692,7 +20208,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr"/>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -19844,7 +20364,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr"/>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -19882,7 +20406,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -20034,7 +20562,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr"/>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -20186,7 +20718,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr"/>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -20224,7 +20760,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr"/>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -20262,7 +20802,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H317" t="inlineStr"/>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -20376,7 +20920,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H320" t="inlineStr"/>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -20490,7 +21038,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H323" t="inlineStr"/>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -20528,7 +21080,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -20566,7 +21122,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H325" t="inlineStr"/>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -20680,7 +21240,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -20794,7 +21358,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr"/>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -20832,7 +21400,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -21402,7 +21974,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -21440,7 +22016,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr"/>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -21478,7 +22058,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H349" t="inlineStr"/>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -21516,7 +22100,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr"/>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -21554,7 +22142,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -21592,7 +22184,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -21630,7 +22226,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -21668,7 +22268,11 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="H354" t="inlineStr"/>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>content_hash is the sha256 of the retained SEC EDGAR company submissions snapshot for this CIK; source_url is the cited 13F filing list</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT56"/>
+  <dimension ref="A1:AT58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8348,6 +8348,262 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MSD Capital, L.P.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Established in 1998, exclusively manages the assets of Michael S. Dell and his family." Discovered via a non-SEC curated-reference lens; classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Private investment firm that exclusively manages the assets of Michael S. Dell and his family.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>MSD Capital utilizes a multi-disciplinary investment strategy focused on maximizing long-term capital appreciation by making investments across the globe in the equities of public and private companies, credit, real estate and other asset classes and securities.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens (Wikipedia's family-office listings); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The family the office serves is named in the classification evidence; it is deliberately NOT recorded as the office's principal, because the site does not name the office's own decision-maker. Wikipedia's family-office category lists this firm under its later corporate name (DFO Management, LLC); the firm's own site presents as MSD Capital, L.P., and the record uses the site's own name — identity verified against that site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Willett Advisors LLC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "manages the philanthropic assets of Michael R. Bloomberg" — a dedicated office serving one named individual. Discovered via a non-SEC curated-reference lens; classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Manages the philanthropic assets of Michael R. Bloomberg.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>The firm's objective is to achieve long-term capital appreciation through the construction of a diversified investment portfolio.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens (Wikipedia's family-office listings); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The family the office serves is named in the classification evidence; it is deliberately NOT recorded as the office's principal, because the site does not name the office's own decision-maker.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8359,7 +8615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H387"/>
+  <dimension ref="A1:H399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23527,6 +23783,462 @@
         </is>
       </c>
       <c r="H387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23539,7 +24251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28091,6 +28803,118 @@
       <c r="F156" t="inlineStr">
         <is>
           <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT58"/>
+  <dimension ref="A1:AT61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8604,6 +8604,350 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Cherng Family Trust</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Cherng Family Trust is the multi-generational family office and investment firm of Andrew and Peggy Cherng (the founders of Panda Express / Panda Restaurant Group) and their family." Discovered via a curated-reference lens; verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Multi-generational family office and investment firm of Andrew and Peggy Cherng, founders of Panda Restaurant Group.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Blue Haven Initiative</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a family office serving one family: "We are a family office investing with high standards, our team is dedicated to using a full complement of capital tools available to leverage our flexibility and multigenerational time horizon." (founders named on the site). Discovered via a curated-reference lens; verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Family office dedicated to putting wealth to work for competitive returns and meaningful impact.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>We believe that solving the world's biggest social and environmental issues requires creative long-term investors who prioritize partnership, patience and continuous learning.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Artémis</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Artémis is the investment company of the Pinault family. Founded in 1992 by François Pinault, it carries out long term investments in companies with strong growth potential." Discovered via a curated-reference lens; verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Investment company of the Pinault family, founded in 1992 by François Pinault; carries out long-term investments in companies with strong growth potential.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Long-term investments in companies with strong growth potential.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Accepted on human review: the automated judge (on a fallback model) missed the site's verbatim opening line, whose construction is identical to the accepted Korys evidence ('the ... investment company of the &lt;family&gt; family'); the overrule and its basis are recorded here for auditability. The site states the firm is French (groupe Artémis); city is not stated and is left blank.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8615,7 +8959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H399"/>
+  <dimension ref="A1:H414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24239,6 +24583,576 @@
         </is>
       </c>
       <c r="H399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24251,7 +25165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F160"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28913,6 +29827,174 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT61"/>
+  <dimension ref="A1:AT62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8948,6 +8948,122 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MacAndrews &amp; Forbes Incorporated</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-owner investment holding: "Wholly owned by Chairman and Chief Executive Officer Ronald O. Perelman" — the diversified investment holding of one named individual, the same class as the accepted KIRKBI and Artémis records. Discovered via a curated-reference lens; verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Diversified investment holding company wholly owned by Ronald O. Perelman.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Our core strategy is to focus our business lines on strong market positions, high quality management with vertical expertise, recognized growth potential and ability to increase profitability.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Perelman is the owner; the site names no separate office decision-maker, so principal fields stay blank. Geography is not stated on the scraped pages and is left blank.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8959,7 +9075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H414"/>
+  <dimension ref="A1:H419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25153,6 +25269,196 @@
         </is>
       </c>
       <c r="H414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25165,7 +25471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29995,6 +30301,62 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -2139,12 +2139,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_15eb1b42d3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Custos Family Office, LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2154,31 +2154,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>We function as our clients’ Chief Financial Officer – protecting their wealth, coordinating financial services through the families’ various stages, and acting as a bridge across generations.</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>https://custosfo.com/</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AUSTIN</t>
+          <t>NEWPORT BEACH</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2188,7 +2180,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>+1 (303) 578-7024</t>
+          <t>+1 (949) 721-2330</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -2219,19 +2211,11 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
         <is>
@@ -2240,7 +2224,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type)</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -2395,12 +2379,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fo_15eb1b42d3</t>
+          <t>fo_4b474eef93</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2421,12 +2405,12 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>NEWPORT BEACH</t>
+          <t>NEW YORK</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2436,7 +2420,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>+1 (949) 721-2330</t>
+          <t>+1 (212) 830-6500</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2635,12 +2619,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fo_4b474eef93</t>
+          <t>fo_3eb2ccad75</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2661,12 +2645,12 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>NEW YORK</t>
+          <t>DENVER</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2676,7 +2660,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>+1 (212) 830-6500</t>
+          <t>+1 (303) 243-5611</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -2895,12 +2879,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fo_3eb2ccad75</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVA Family Office, LLC</t>
+          <t>Custos Family Office, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2910,23 +2894,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>We function as our clients’ Chief Financial Officer – protecting their wealth, coordinating financial services through the families’ various stages, and acting as a bridge across generations.</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://custosfo.com/</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>DENVER</t>
+          <t>AUSTIN</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2936,7 +2928,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>+1 (303) 243-5611</t>
+          <t>+1 (303) 578-7024</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -2967,11 +2959,19 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -3635,12 +3635,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fo_89137929e9</t>
+          <t>fo_685bea3a32</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BOSTON FAMILY OFFICE LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3661,12 +3661,12 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>BOSTON</t>
+          <t>MINNETONKA</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>+1 (617) 624-0800</t>
+          <t>+1 (952) 841-0400</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -3875,12 +3875,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_89137929e9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>BOSTON FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3890,31 +3890,23 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Investments Our in-house investment team will craft custom, goals-based, and integrated strategies to not just keep your wealth, but grow it.</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>https://fortitudefo.com/</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>SCOTTSDALE</t>
+          <t>BOSTON</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3924,7 +3916,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>+1 (602) 834-0089</t>
+          <t>+1 (617) 624-0800</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -3955,19 +3947,11 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
       <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr">
         <is>
@@ -3976,7 +3960,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type)</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -4144,12 +4128,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fo_29e17a89bc</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, LLC</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4159,23 +4143,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Investments Our in-house investment team will craft custom, goals-based, and integrated strategies to not just keep your wealth, but grow it.</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://fortitudefo.com/</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>NORTH MIAMI BEACH</t>
+          <t>SCOTTSDALE</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4185,7 +4177,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>+1 (305) 935-5502</t>
+          <t>+1 (602) 834-0089</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -4216,11 +4208,19 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -4384,12 +4384,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fo_685bea3a32</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Callan Family Office, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4399,23 +4399,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>A partnership of entrepreneurs serving entrepreneurial families, Callan Family Office’s 23 partners have decades of experience working exclusively with ultra-high-net-worth families across generations. We operate as an independent firm, offering tailored, open-architecture solutions that integrate seamlessly into every aspect of your financial life. As a fiduciary, we are committed to prioritizing</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Get Started Tax-Focused Planning and Investments For ultra-high-net-worth families, tax-efficient investment and planning are paramount to growing and preserving wealth across generations.</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://callanfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>MINNETONKA</t>
+          <t>RADNOR</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4425,7 +4437,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>+1 (952) 841-0400</t>
+          <t>+1 (267) 250-2036</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -4456,11 +4468,19 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
       <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr">
         <is>
@@ -4469,7 +4489,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -4624,12 +4644,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_29e17a89bc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Callan Family Office, LLC</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4639,35 +4659,23 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>A partnership of entrepreneurs serving entrepreneurial families, Callan Family Office’s 23 partners have decades of experience working exclusively with ultra-high-net-worth families across generations. We operate as an independent firm, offering tailored, open-architecture solutions that integrate seamlessly into every aspect of your financial life. As a fiduciary, we are committed to prioritizing</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Get Started Tax-Focused Planning and Investments For ultra-high-net-worth families, tax-efficient investment and planning are paramount to growing and preserving wealth across generations.</t>
-        </is>
-      </c>
+          <t>SEC 13F filer self-identifying as a family office; SEC Form ADV / IAPD registration names it a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>https://callanfamilyoffice.com/</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>RADNOR</t>
+          <t>NORTH MIAMI BEACH</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4677,7 +4685,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>+1 (267) 250-2036</t>
+          <t>+1 (305) 935-5502</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
@@ -4708,19 +4716,11 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings) (firm existence, address, phone, EIN); SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type)</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -11345,7 +11345,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_15eb1b42d3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001904423.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001599603.json</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11383,7 +11383,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_15eb1b42d3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001904423.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001599603.json</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11421,7 +11421,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_15eb1b42d3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001904423.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001599603.json</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11459,12 +11459,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_a4cb68cd35</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -11474,17 +11474,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>fetched firm website</t>
+          <t>firm website</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://custosfo.com/</t>
+          <t>https://matterfamilyoffice.com</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -11497,32 +11497,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_a4cb68cd35</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>investment_thesis</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>firm website (stated investment approach / mission)</t>
+          <t>IAPD registration record</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://custosfo.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/106806</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -11550,17 +11550,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>firm website</t>
+          <t>fetched firm website</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://matterfamilyoffice.com</t>
+          <t>https://www.matterfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -11578,27 +11578,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>IAPD registration record</t>
+          <t>website meta description</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/106806</t>
+          <t>https://www.matterfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>investment_thesis</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>fetched firm website</t>
+          <t>firm website (stated investment approach / mission)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -11649,32 +11649,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>fo_a4cb68cd35</t>
+          <t>fo_4b474eef93</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>website meta description</t>
+          <t>SEC EDGAR submissions (registrant name)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.matterfamilyoffice.com/</t>
+          <t>https://data.sec.gov/submissions/CIK0001536411.json</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -11687,32 +11687,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>fo_a4cb68cd35</t>
+          <t>fo_4b474eef93</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>investment_thesis</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>firm website (stated investment approach / mission)</t>
+          <t>SEC EDGAR submissions (business address)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.matterfamilyoffice.com/</t>
+          <t>https://data.sec.gov/submissions/CIK0001536411.json</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -11725,12 +11725,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>fo_15eb1b42d3</t>
+          <t>fo_4b474eef93</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>hq_phone</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (registrant name)</t>
+          <t>SEC EDGAR submissions (business phone)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001599603.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001536411.json</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -11763,32 +11763,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>fo_15eb1b42d3</t>
+          <t>fo_55e904bc2b</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business address)</t>
+          <t>firm website</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001599603.json</t>
+          <t>https://sestantefo.com</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -11801,27 +11801,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>fo_15eb1b42d3</t>
+          <t>fo_55e904bc2b</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>hq_phone</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business phone)</t>
+          <t>IAPD registration record</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001599603.json</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/335152</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -11854,17 +11854,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>firm website</t>
+          <t>fetched firm website</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://sestantefamilyoffice.com</t>
+          <t>http://sestante.com/</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -11882,27 +11882,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>IAPD registration record</t>
+          <t>website meta description</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/335152</t>
+          <t>http://sestante.com/</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>investment_thesis</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>fetched firm website</t>
+          <t>firm website (stated investment approach / mission)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -11953,32 +11953,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>fo_55e904bc2b</t>
+          <t>fo_3eb2ccad75</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>website meta description</t>
+          <t>SEC EDGAR submissions (registrant name)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>http://sestante.com/</t>
+          <t>https://data.sec.gov/submissions/CIK0001802084.json</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -11991,32 +11991,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>fo_55e904bc2b</t>
+          <t>fo_3eb2ccad75</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>investment_thesis</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>firm website (stated investment approach / mission)</t>
+          <t>SEC EDGAR submissions (business address)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>http://sestante.com/</t>
+          <t>https://data.sec.gov/submissions/CIK0001802084.json</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -12029,12 +12029,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>fo_4b474eef93</t>
+          <t>fo_3eb2ccad75</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>hq_phone</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -12044,12 +12044,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (registrant name)</t>
+          <t>SEC EDGAR submissions (business phone)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001536411.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001802084.json</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -12067,32 +12067,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>fo_4b474eef93</t>
+          <t>fo_f638fbd06f</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business address)</t>
+          <t>firm website</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001536411.json</t>
+          <t>https://storyonefamilyoffice.com</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -12105,27 +12105,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>fo_4b474eef93</t>
+          <t>fo_f638fbd06f</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>hq_phone</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business phone)</t>
+          <t>IAPD registration record</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001536411.json</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -12158,17 +12158,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>firm website</t>
+          <t>fetched firm website</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://storyonefamilyoffice.com</t>
+          <t>https://story-one.com/</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -12186,27 +12186,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>IAPD registration record</t>
+          <t>website meta description</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
+          <t>https://story-one.com/</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>investment_thesis</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>fetched firm website</t>
+          <t>firm website (stated investment approach / mission)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -12262,27 +12262,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>estimated_aum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>website meta description</t>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://story-one.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -12300,27 +12300,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>investment_thesis</t>
+          <t>principal_name</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>firm website (stated investment approach / mission)</t>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://story-one.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>estimated_aum</t>
+          <t>principal_title</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -12371,27 +12371,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>fo_f638fbd06f</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>principal_name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+          <t>SEC EDGAR submissions (registrant name)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
+          <t>https://data.sec.gov/submissions/CIK0001904423.json</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -12409,27 +12409,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>fo_f638fbd06f</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>principal_title</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+          <t>SEC EDGAR submissions (business address)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
+          <t>https://data.sec.gov/submissions/CIK0001904423.json</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -12447,12 +12447,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>fo_3eb2ccad75</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>hq_phone</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (registrant name)</t>
+          <t>SEC EDGAR submissions (business phone)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001802084.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001904423.json</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -12485,27 +12485,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>fo_3eb2ccad75</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business address)</t>
+          <t>fetched firm website</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001802084.json</t>
+          <t>https://custosfo.com/</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -12523,32 +12523,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>fo_3eb2ccad75</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>hq_phone</t>
+          <t>investment_thesis</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business phone)</t>
+          <t>firm website (stated investment approach / mission)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001802084.json</t>
+          <t>https://custosfo.com/</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -13473,7 +13473,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>fo_89137929e9</t>
+          <t>fo_685bea3a32</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001039807.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001683689.json</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -13511,7 +13511,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>fo_89137929e9</t>
+          <t>fo_685bea3a32</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001039807.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001683689.json</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -13549,7 +13549,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>fo_89137929e9</t>
+          <t>fo_685bea3a32</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001039807.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001683689.json</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -13777,7 +13777,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_89137929e9</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001950506.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001039807.json</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -13815,7 +13815,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_89137929e9</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001950506.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001039807.json</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -13853,7 +13853,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_89137929e9</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001950506.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001039807.json</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -13891,12 +13891,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_80f649ced1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -13906,17 +13906,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>fetched firm website</t>
+          <t>firm website</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://fortitudefo.com/</t>
+          <t>https://dcafamilyoffice.com</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -13929,32 +13929,32 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_80f649ced1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>investment_thesis</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>firm website (stated investment approach / mission)</t>
+          <t>IAPD registration record</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://fortitudefo.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -13972,7 +13972,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -13982,17 +13982,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>firm website</t>
+          <t>fetched firm website</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://dcafamilyoffice.com</t>
+          <t>https://dcafamilyoffice.com/</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -14010,27 +14010,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>IAPD registration record</t>
+          <t>website meta description</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+          <t>https://dcafamilyoffice.com/</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -14048,22 +14048,22 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>estimated_aum</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>fetched firm website</t>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://dcafamilyoffice.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -14086,27 +14086,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>principal_name</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>website meta description</t>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://dcafamilyoffice.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>estimated_aum</t>
+          <t>principal_title</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -14157,27 +14157,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>fo_80f649ced1</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>principal_name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+          <t>SEC EDGAR submissions (registrant name)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+          <t>https://data.sec.gov/submissions/CIK0001950506.json</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -14195,27 +14195,27 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>fo_80f649ced1</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>principal_title</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+          <t>SEC EDGAR submissions (business address)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+          <t>https://data.sec.gov/submissions/CIK0001950506.json</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -14233,12 +14233,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>fo_29e17a89bc</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>hq_phone</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -14248,12 +14248,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (registrant name)</t>
+          <t>SEC EDGAR submissions (business phone)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0002135110.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001950506.json</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -14271,27 +14271,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>fo_29e17a89bc</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business address)</t>
+          <t>fetched firm website</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0002135110.json</t>
+          <t>https://fortitudefo.com/</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -14309,32 +14309,32 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>fo_29e17a89bc</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>hq_phone</t>
+          <t>investment_thesis</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business phone)</t>
+          <t>firm website (stated investment approach / mission)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0002135110.json</t>
+          <t>https://fortitudefo.com/</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -14537,7 +14537,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>fo_685bea3a32</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001683689.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001938970.json</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -14575,7 +14575,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>fo_685bea3a32</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001683689.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001938970.json</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -14613,7 +14613,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>fo_685bea3a32</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -14633,7 +14633,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001683689.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001938970.json</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -14651,12 +14651,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>fo_3171716a52</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -14666,17 +14666,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>firm website</t>
+          <t>fetched firm website</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://angelesfamilyoffice.com</t>
+          <t>https://callanfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -14689,32 +14689,32 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>fo_3171716a52</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>IAPD registration record</t>
+          <t>website meta description</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/338266</t>
+          <t>https://callanfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -14727,12 +14727,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>fo_3171716a52</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>investment_thesis</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -14742,17 +14742,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>fetched firm website</t>
+          <t>firm website (stated investment approach / mission)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://www.angelesinvestments.com/</t>
+          <t>https://callanfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -14780,12 +14780,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>website meta description</t>
+          <t>firm website</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://www.angelesinvestments.com/</t>
+          <t>https://angelesfamilyoffice.com</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -14808,27 +14808,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>investment_thesis</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>firm website (stated investment approach / mission)</t>
+          <t>IAPD registration record</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://www.angelesinvestments.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/338266</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -14841,27 +14841,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_3171716a52</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (registrant name)</t>
+          <t>fetched firm website</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001938970.json</t>
+          <t>https://www.angelesinvestments.com/</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -14879,32 +14879,32 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_3171716a52</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>hq_country</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business address)</t>
+          <t>website meta description</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001938970.json</t>
+          <t>https://www.angelesinvestments.com/</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -14917,32 +14917,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_3171716a52</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>hq_phone</t>
+          <t>investment_thesis</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SEC EDGAR submissions (business phone)</t>
+          <t>firm website (stated investment approach / mission)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001938970.json</t>
+          <t>https://www.angelesinvestments.com/</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -14955,27 +14955,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_29e17a89bc</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>fetched firm website</t>
+          <t>SEC EDGAR submissions (registrant name)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com/</t>
+          <t>https://data.sec.gov/submissions/CIK0002135110.json</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -14993,32 +14993,32 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_29e17a89bc</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>hq_country</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>website meta description</t>
+          <t>SEC EDGAR submissions (business address)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com/</t>
+          <t>https://data.sec.gov/submissions/CIK0002135110.json</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -15031,32 +15031,32 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_29e17a89bc</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>investment_thesis</t>
+          <t>hq_phone</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>firm website (stated investment approach / mission)</t>
+          <t>SEC EDGAR submissions (business phone)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com/</t>
+          <t>https://data.sec.gov/submissions/CIK0002135110.json</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -21967,7 +21967,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_15eb1b42d3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -21987,7 +21987,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001904423.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001599603.json</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -21999,7 +21999,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_15eb1b42d3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/294025</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/106079</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -22031,29 +22031,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_15eb1b42d3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>family-office status, type</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://custosfo.com/</t>
-        </is>
-      </c>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22063,21 +22055,29 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>fo_9220a272d8</t>
+          <t>fo_a4cb68cd35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/106806</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22097,17 +22097,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>firm registration, family-office status, type</t>
+          <t>family-office status, type</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/106806</t>
+          <t>https://www.matterfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -22124,24 +22124,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>family-office status, type</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://www.matterfamilyoffice.com/</t>
-        </is>
-      </c>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22151,21 +22143,29 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>fo_a4cb68cd35</t>
+          <t>fo_4b474eef93</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>firm existence, address, phone, EIN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/submissions/CIK0001536411.json</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22175,7 +22175,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>fo_15eb1b42d3</t>
+          <t>fo_4b474eef93</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22185,17 +22185,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>firm existence, address, phone, EIN</t>
+          <t>firm registration, family-office status, type</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001599603.json</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/326761</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -22207,29 +22207,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>fo_15eb1b42d3</t>
+          <t>fo_4b474eef93</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>firm registration, family-office status, type</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/106079</t>
-        </is>
-      </c>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22239,21 +22231,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fo_15eb1b42d3</t>
+          <t>fo_55e904bc2b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/335152</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22273,17 +22273,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>firm registration, family-office status, type</t>
+          <t>family-office status, type</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/335152</t>
+          <t>http://sestante.com/</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -22300,24 +22300,16 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>family-office status, type</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>http://sestante.com/</t>
-        </is>
-      </c>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22327,21 +22319,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>fo_55e904bc2b</t>
+          <t>fo_3eb2ccad75</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>firm existence, address, phone, EIN</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/submissions/CIK0001802084.json</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22351,7 +22351,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>fo_4b474eef93</t>
+          <t>fo_3eb2ccad75</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -22361,17 +22361,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>firm existence, address, phone, EIN</t>
+          <t>firm registration, family-office status, type</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001536411.json</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/285035</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -22383,29 +22383,21 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>fo_4b474eef93</t>
+          <t>fo_3eb2ccad75</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>firm registration, family-office status, type</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/326761</t>
-        </is>
-      </c>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22415,21 +22407,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fo_4b474eef93</t>
+          <t>fo_f638fbd06f</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22449,17 +22449,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>firm registration, family-office status, type</t>
+          <t>family-office status, type</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
+          <t>https://story-one.com/</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -22481,17 +22481,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>family-office status, type</t>
+          <t>total regulatory AUM (ADV Item 5.F), owner/control person (ADV Schedule A)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://story-one.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -22508,7 +22508,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -22516,16 +22516,8 @@
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>total regulatory AUM (ADV Item 5.F), owner/control person (ADV Schedule A)</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/331394</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22535,21 +22527,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fo_f638fbd06f</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>firm existence, address, phone, EIN</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/submissions/CIK0001904423.json</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -22559,7 +22559,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fo_3eb2ccad75</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -22569,17 +22569,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>firm existence, address, phone, EIN</t>
+          <t>firm registration, family-office status, type</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001802084.json</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/294025</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -22591,7 +22591,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fo_3eb2ccad75</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -22601,17 +22601,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>firm registration, family-office status, type</t>
+          <t>family-office status, type</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/285035</t>
+          <t>https://custosfo.com/</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -22623,7 +22623,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fo_3eb2ccad75</t>
+          <t>fo_9220a272d8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -23151,7 +23151,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>fo_89137929e9</t>
+          <t>fo_685bea3a32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001039807.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001683689.json</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -23183,7 +23183,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>fo_89137929e9</t>
+          <t>fo_685bea3a32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -23203,7 +23203,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/107141</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/326761</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -23215,7 +23215,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>fo_89137929e9</t>
+          <t>fo_685bea3a32</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -23327,7 +23327,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_89137929e9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -23347,7 +23347,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001950506.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001039807.json</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -23359,7 +23359,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_89137929e9</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/317615</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/107141</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -23391,29 +23391,21 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_89137929e9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Firm Website</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>family-office status, type</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>https://fortitudefo.com/</t>
-        </is>
-      </c>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -23423,21 +23415,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>fo_da95e70bda</t>
+          <t>fo_80f649ced1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -23457,17 +23457,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>firm registration, family-office status, type</t>
+          <t>family-office status, type</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+          <t>https://dcafamilyoffice.com/</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -23489,17 +23489,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>family-office status, type</t>
+          <t>total regulatory AUM (ADV Item 5.F), owner/control person (ADV Schedule A)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://dcafamilyoffice.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -23524,16 +23524,8 @@
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>total regulatory AUM (ADV Item 5.F), owner/control person (ADV Schedule A)</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -23543,21 +23535,29 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>fo_80f649ced1</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>firm existence, address, phone, EIN</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/submissions/CIK0001950506.json</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -23567,7 +23567,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>fo_29e17a89bc</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -23577,17 +23577,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>firm existence, address, phone, EIN</t>
+          <t>firm registration, family-office status, type</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0002135110.json</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/317615</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -23599,7 +23599,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>fo_29e17a89bc</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -23609,17 +23609,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>Firm Website</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>firm registration, family-office status, type</t>
+          <t>family-office status, type</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/142856</t>
+          <t>https://fortitudefo.com/</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -23631,7 +23631,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>fo_29e17a89bc</t>
+          <t>fo_da95e70bda</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -23743,7 +23743,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>fo_685bea3a32</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -23763,7 +23763,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001683689.json</t>
+          <t>https://data.sec.gov/submissions/CIK0001938970.json</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -23775,7 +23775,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>fo_685bea3a32</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/326761</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/317446</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -23807,21 +23807,29 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>fo_685bea3a32</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://callanfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -23831,29 +23839,21 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>fo_3171716a52</t>
+          <t>fo_beb7590905</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>firm registration, family-office status, type</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/338266</t>
-        </is>
-      </c>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -23873,17 +23873,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>family-office status, type</t>
+          <t>firm registration, family-office status, type</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.angelesinvestments.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/338266</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -23900,16 +23900,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>discovery</t>
+          <t>verification</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.angelesinvestments.com/</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -23919,29 +23927,21 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_3171716a52</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>verification</t>
+          <t>discovery</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SEC EDGAR (13F / SC / Form D filings)</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>firm existence, address, phone, EIN</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://data.sec.gov/submissions/CIK0001938970.json</t>
-        </is>
-      </c>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>2026-08-08</t>
@@ -23951,7 +23951,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_29e17a89bc</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -23961,17 +23961,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+          <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>firm registration, family-office status, type</t>
+          <t>firm existence, address, phone, EIN</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/317446</t>
+          <t>https://data.sec.gov/submissions/CIK0002135110.json</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -23983,7 +23983,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_29e17a89bc</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -23993,17 +23993,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Firm Website</t>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>family-office status, type</t>
+          <t>firm registration, family-office status, type</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com/</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/142856</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -24015,7 +24015,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>fo_beb7590905</t>
+          <t>fo_29e17a89bc</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT69"/>
+  <dimension ref="A1:AT81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9040,6 +9040,1458 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>fo_41fc928853</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ARAGON FAMILY OFFICE LLC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV registration or the firm's own website identifies it as a family office. It is an ACTIVE SEC-registered investment adviser (IAPD CRD 337597). Under the SEC Family Office Rule (17 CFR 275.202(a)(11)(G)-1) a bona-fide single-family office is excluded from adviser registration, so an actively-registered family-office adviser serves clients beyond one family -&gt; multi-family office.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://aragonfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>HOMEWOOD</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address)</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited â€” disclosed, not fabricated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FinanciÃ¨re Agache</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Le groupe familial Arnault dÃ©tenant au total 97,5% de Christian Dior". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Holding company of the Arnault family, controlling shareholder of Christian Dior.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Florian Ollivier</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>PrÃ©sident-directeur gÃ©nÃ©ral</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status/type, description, principal)</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KIRKBI</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "As the holding company of the Kirk Kristiansen family, who founded the LEGO Group in 1932". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Holding and investment company of the Kirk Kristiansen family, founders of the LEGO Group; owns and develops businesses for the long term.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Billund</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status/type, description, principal)</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone; principal_name; principal_title</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Controlled by the Kirk Kristiansen family; no individual decision-maker is named on the site, so the principal is left could_not_verify. The firm also appears in SEC EDGAR full-text filings (Schedule 13D/13G on US holdings), corroborating its investing activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Prime Opportunities Investment Group</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>An authoritative source (SEC Form 13F filing / SEC IAPD Form ADV registration, or the firm's own website) identifies it as a family office; single vs multi family not established from an authoritative source (adviser-registration status not verifiable by an exact identifier), so honestly labelled Undetermined rather than guessed.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>US single-family office investing in public equities with a private-equity approach; roots in real-estate holdings and operating businesses.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>We invest only in publicly traded companies, and take a private equity approach to our investment process.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Pouya David Yadegar</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Founder, Chief Investment Officer</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status/type, description, principal)</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Self-describes as a single-family office; a smaller, public-equity focused firm â€” held at Low confidence pending a second authoritative source. Classification corrected Single-Family Office -&gt; Undetermined on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Korys</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Korys is the entrepreneurial investment company of the Colruyt family.". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Entrepreneurial investment company of the Colruyt family, investing in companies aligned with conscious-consumer solutions.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Korys invests in companies that offer solutions to the challenges conscious consumers face in their search for products and services.</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status/type, description, principal)</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone; principal_name; principal_title</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Controlled by the Colruyt family; no individual decision-maker is named on the site, so the principal is left could_not_verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Builders Vision</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Lukas Walton founded Builders Vision in 2018, inspired by the belief that philanthropy and investing together can shift capital markets toward sustainable solutions.". Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Impact platform founded by Lukas Walton in 2018 that combines philanthropy and investing to shift capital markets toward sustainable solutions.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Lukas Walton</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status/type, description, principal)</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr">
+        <is>
+          <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The firm also appears in SEC EDGAR full-text filings on US holdings, corroborating its investing activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MSD Capital, L.P.</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Established in 1998, exclusively manages the assets of Michael S. Dell and his family." Discovered via a non-SEC curated-reference lens; classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Private investment firm that exclusively manages the assets of Michael S. Dell and his family.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MSD Capital utilizes a multi-disciplinary investment strategy focused on maximizing long-term capital appreciation by making investments across the globe in the equities of public and private companies, credit, real estate and other asset classes and securities.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens (Wikipedia's family-office listings); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The family the office serves is named in the classification evidence; it is deliberately NOT recorded as the office's principal, because the site does not name the office's own decision-maker. Wikipedia's family-office category lists this firm under its later corporate name (DFO Management, LLC); the firm's own site presents as MSD Capital, L.P., and the record uses the site's own name â€” identity verified against that site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Willett Advisors LLC</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "manages the philanthropic assets of Michael R. Bloomberg" â€” a dedicated office serving one named individual. Discovered via a non-SEC curated-reference lens; classification and firm identity verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Manages the philanthropic assets of Michael R. Bloomberg.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>The firm's objective is to achieve long-term capital appreciation through the construction of a diversified investment portfolio.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens (Wikipedia's family-office listings); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The family the office serves is named in the classification evidence; it is deliberately NOT recorded as the office's principal, because the site does not name the office's own decision-maker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cherng Family Trust</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "Cherng Family Trust is the multi-generational family office and investment firm of Andrew and Peggy Cherng (the founders of Panda Express / Panda Restaurant Group) and their family." Discovered via a curated-reference lens; verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Multi-generational family office and investment firm of Andrew and Peggy Cherng, founders of Panda Restaurant Group.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Blue Haven Initiative</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a family office serving one family: "We are a family office investing with high standards, our team is dedicated to using a full complement of capital tools available to leverage our flexibility and multigenerational time horizon." (founders named on the site). Discovered via a curated-reference lens; verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Family office dedicated to putting wealth to work for competitive returns and meaningful impact.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>We believe that solving the world's biggest social and environmental issues requires creative long-term investors who prioritize partnership, patience and continuous learning.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ArtÃ©mis</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-family office: "ArtÃ©mis is the investment company of the Pinault family. Founded in 1992 by FranÃ§ois Pinault, it carries out long term investments in companies with strong growth potential." Discovered via a curated-reference lens; verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Investment company of the Pinault family, founded in 1992 by FranÃ§ois Pinault; carries out long-term investments in companies with strong growth potential.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Long-term investments in companies with strong growth potential.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Accepted on human review: the automated judge (on a fallback model) missed the site's verbatim opening line, whose construction is identical to the accepted Korys evidence ('the ... investment company of the &lt;family&gt; family'); the overrule and its basis are recorded here for auditability. The site states the firm is French (groupe ArtÃ©mis); city is not stated and is left blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MacAndrews &amp; Forbes Incorporated</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Firm's own website self-identifies as a single-owner investment holding: "Wholly owned by Chairman and Chief Executive Officer Ronald O. Perelman" â€” the diversified investment holding of one named individual, the same class as the accepted KIRKBI and ArtÃ©mis records. Discovered via a curated-reference lens; verified against the firm's own website.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Diversified investment holding company wholly owned by Ronald O. Perelman.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Our core strategy is to focus our business lines on strong market positions, high quality management with vertical expertise, recognized growth potential and ability to increase profitability.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>Firm Website (single-family-office status, firm identity)</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr">
+        <is>
+          <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Perelman is the owner; the site names no separate office decision-maker, so principal fields stay blank. Geography is not stated on the scraped pages and is left blank.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9051,7 +10503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H376"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23345,6 +24797,2628 @@
         </is>
       </c>
       <c r="H376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>fo_41fc928853</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV registration (firm summary)</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/337597</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>fo_41fc928853</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://aragonfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>fo_41fc928853</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV registration (firm summary)</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/337597</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>fo_41fc928853</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV registration (firm summary)</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/337597</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>principal_name</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>firm website (leadership/about page)</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>principal_title</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>firm website (leadership/about page)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>principal_name</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>firm website (leadership/about page)</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>principal_title</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>firm website (leadership/about page)</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>principal_name</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>firm website (leadership/about page)</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>principal_title</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>firm website (leadership/about page)</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>firm website (scrape + extraction)</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>fo_type_evidence</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>firm website (Firecrawl scrape + verification)</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23357,7 +27431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29309,6 +33383,678 @@
       <c r="F203" t="inlineStr">
         <is>
           <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>fo_41fc928853</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>family-office registration, firm identity &amp; office address</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/337597</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>fo_41fc928853</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>https://www.financiereagache-finance.com/</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>fo_ca957ee5d5</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>fo_d27cc088a3</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>https://www.primeopp.com/</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>fo_a750611281</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>https://www.korys.be/</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>fo_3642e17ac1</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>family-office status/type, description, principal</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>https://www.buildersvision.com/</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>fo_e8d9f15c57</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>https://www.msdcapital.com/</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>fo_207554cfe7</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>https://www.willettadvisors.com/</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>fo_d80fbfc1d9</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.cherngfamilytrust.com/</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>fo_f36be5c2a3</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.bluehaveninitiative.com/</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>fo_e2b48bb2d2</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.groupeartemis.com/</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>fo_68c2c35a95</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>single-family-office status, firm identity</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.macandrewsandforbes.com/</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>fo_e6bc01c928</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Curated directory / reference (Wikipedia, associations)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT81"/>
+  <dimension ref="A1:AW81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,130 +523,145 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>firm_contact_email_status</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>recent_signal_1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>recent_signal_1_date</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>recent_signal_1_source</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>recent_signal_2</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>recent_signal_2_date</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>recent_signal_2_source</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>recent_signal_3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>recent_signal_3_date</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>recent_signal_3_source</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name_confidence</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>fo_type_confidence</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>principal_name_confidence</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>principal_email_confidence</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>principal_phone_confidence</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>firm_contact_email_confidence</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>website_confidence</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>corporate_linkedin_confidence</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>principal_linkedin_confidence</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>estimated_aum_confidence</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>investment_thesis_confidence</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>recent_activity_confidence</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>discovery_source</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>verification_sources</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>record_confidence</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>data_as_of</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>could_not_verify</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>reviewer_notes</t>
         </is>
@@ -726,59 +741,62 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr">
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -866,28 +884,24 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
@@ -895,38 +909,45 @@
           <t>High</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
         </is>
@@ -990,55 +1011,58 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1110,55 +1134,58 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -1246,28 +1273,24 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
@@ -1275,38 +1298,45 @@
           <t>High</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
         </is>
@@ -1374,59 +1404,62 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr">
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr">
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="AT7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1490,18 +1523,18 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
@@ -1509,32 +1542,35 @@
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="AT8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -1610,59 +1646,62 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr">
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
         </is>
@@ -1730,18 +1769,18 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
@@ -1749,32 +1788,35 @@
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="AT10" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -1854,59 +1896,62 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm Classification corrected Single-Family Office -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
         </is>
@@ -1974,18 +2019,18 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
@@ -1993,32 +2038,35 @@
       <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -2082,55 +2130,58 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr">
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr">
+      <c r="AT13" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office [registration status] SEC IAPD registration (CRD 329017) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via an independently verified firm website. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
         </is>
@@ -2198,18 +2249,18 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
@@ -2217,32 +2268,35 @@
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr">
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="AW14" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -2318,59 +2372,62 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr">
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AS15" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="AT15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
+      <c r="AW15" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -2438,18 +2495,18 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
@@ -2457,32 +2514,35 @@
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr">
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
+      <c r="AS16" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="AT16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT16" t="inlineStr">
+      <c r="AW16" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -2558,59 +2618,62 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr">
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr">
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
+      <c r="AW17" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -2678,18 +2741,18 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
@@ -2697,32 +2760,35 @@
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr">
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -2810,28 +2876,24 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AH19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="inlineStr">
@@ -2839,38 +2901,45 @@
           <t>High</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
+      <c r="AS19" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr">
+      <c r="AT19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="AW19" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm</t>
         </is>
@@ -2946,59 +3015,62 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr">
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr">
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP20" t="inlineStr">
+      <c r="AS20" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ20" t="inlineStr">
+      <c r="AT20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="AW20" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -3082,28 +3154,24 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AH21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr">
@@ -3115,30 +3183,37 @@
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr">
+      <c r="AS21" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ21" t="inlineStr">
+      <c r="AT21" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
+      <c r="AW21" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm</t>
         </is>
@@ -3218,59 +3293,62 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr">
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr">
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP22" t="inlineStr">
+      <c r="AS22" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr">
+      <c r="AT22" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
+      <c r="AW22" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -3346,59 +3424,62 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr">
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr">
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP23" t="inlineStr">
+      <c r="AS23" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="AT23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
+      <c r="AW23" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -3466,18 +3547,18 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
@@ -3485,32 +3566,35 @@
       <c r="AL24" t="inlineStr"/>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr">
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP24" t="inlineStr">
+      <c r="AS24" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr">
+      <c r="AT24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
+      <c r="AW24" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -3578,55 +3662,58 @@
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr">
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP25" t="inlineStr">
+      <c r="AS25" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ25" t="inlineStr">
+      <c r="AT25" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
+      <c r="AW25" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -3694,18 +3781,18 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
@@ -3713,32 +3800,35 @@
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr">
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP26" t="inlineStr">
+      <c r="AS26" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ26" t="inlineStr">
+      <c r="AT26" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr">
+      <c r="AW26" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -3814,59 +3904,62 @@
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr">
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr">
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP27" t="inlineStr">
+      <c r="AS27" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ27" t="inlineStr">
+      <c r="AT27" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
+      <c r="AW27" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office CORRECTION (2026-07-28): the firm's generic name had caused an unrelated company's website (thefamilyoffice.com, a residential real-estate advisory) to be attached; all website-derived fields were removed. Retained facts are IAPD-verified only. SEC registration confirmed inactive/withdrawn (IAPD firm search, 2026-07-28).</t>
         </is>
@@ -3934,18 +4027,18 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
@@ -3953,32 +4046,35 @@
       <c r="AL28" t="inlineStr"/>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr">
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP28" t="inlineStr">
+      <c r="AS28" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ28" t="inlineStr">
+      <c r="AT28" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr">
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT28" t="inlineStr">
+      <c r="AW28" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -4062,28 +4158,24 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
       <c r="AL29" t="inlineStr">
@@ -4095,30 +4187,37 @@
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr">
+        <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP29" t="inlineStr">
+      <c r="AS29" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ29" t="inlineStr">
+      <c r="AT29" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT29" t="inlineStr">
+      <c r="AW29" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm</t>
         </is>
@@ -4194,59 +4293,62 @@
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr">
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr">
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP30" t="inlineStr">
+      <c r="AS30" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ30" t="inlineStr">
+      <c r="AT30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT30" t="inlineStr">
+      <c r="AW30" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -4322,59 +4424,62 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr">
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr">
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP31" t="inlineStr">
+      <c r="AS31" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ31" t="inlineStr">
+      <c r="AT31" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT31" t="inlineStr">
+      <c r="AW31" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -4454,59 +4559,62 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr">
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr">
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP32" t="inlineStr">
+      <c r="AS32" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ32" t="inlineStr">
+      <c r="AT32" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr">
+      <c r="AW32" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -4582,59 +4690,62 @@
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr">
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr">
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP33" t="inlineStr">
+      <c r="AS33" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ33" t="inlineStr">
+      <c r="AT33" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT33" t="inlineStr">
+      <c r="AW33" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -4702,18 +4813,18 @@
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
@@ -4721,32 +4832,35 @@
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr">
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP34" t="inlineStr">
+      <c r="AS34" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ34" t="inlineStr">
+      <c r="AT34" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr">
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT34" t="inlineStr">
+      <c r="AW34" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -4818,55 +4932,58 @@
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr">
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP35" t="inlineStr">
+      <c r="AS35" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ35" t="inlineStr">
+      <c r="AT35" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT35" t="inlineStr">
+      <c r="AW35" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office Classification corrected Undetermined -&gt; Multi-Family Office on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
         </is>
@@ -4934,18 +5051,18 @@
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
@@ -4953,32 +5070,35 @@
       <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr">
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP36" t="inlineStr">
+      <c r="AS36" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ36" t="inlineStr">
+      <c r="AT36" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr">
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT36" t="inlineStr">
+      <c r="AW36" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -5066,28 +5186,24 @@
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr">
+      <c r="AH37" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr">
@@ -5095,38 +5211,45 @@
           <t>High</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr">
+        <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP37" t="inlineStr">
+      <c r="AS37" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ37" t="inlineStr">
+      <c r="AT37" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT37" t="inlineStr">
+      <c r="AW37" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm</t>
         </is>
@@ -5194,18 +5317,18 @@
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
@@ -5213,32 +5336,35 @@
       <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr">
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP38" t="inlineStr">
+      <c r="AS38" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ38" t="inlineStr">
+      <c r="AT38" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr">
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT38" t="inlineStr">
+      <c r="AW38" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -5322,28 +5448,24 @@
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF39" t="inlineStr">
+      <c r="AH39" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
       <c r="AL39" t="inlineStr">
@@ -5351,38 +5473,45 @@
           <t>High</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr">
+        <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP39" t="inlineStr">
+      <c r="AS39" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ39" t="inlineStr">
+      <c r="AT39" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr">
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT39" t="inlineStr">
+      <c r="AW39" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm</t>
         </is>
@@ -5462,59 +5591,62 @@
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF40" t="inlineStr">
+      <c r="AH40" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AL40" t="inlineStr"/>
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr">
+        <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP40" t="inlineStr">
+      <c r="AS40" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ40" t="inlineStr">
+      <c r="AT40" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr">
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
         </is>
       </c>
-      <c r="AT40" t="inlineStr">
+      <c r="AW40" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm [registration status] SEC IAPD registration (CRD 134062) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via SEC Form ADV Item 5.F regulatory AUM and Form 13F filings. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
         </is>
@@ -5582,55 +5714,58 @@
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr">
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP41" t="inlineStr">
+      <c r="AS41" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ41" t="inlineStr">
+      <c r="AT41" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS41" t="inlineStr">
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT41" t="inlineStr">
+      <c r="AW41" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office [registration status] SEC IAPD registration (CRD 158123) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via an independently verified firm website. (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
         </is>
@@ -5698,18 +5833,18 @@
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
@@ -5717,32 +5852,35 @@
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr">
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP42" t="inlineStr">
+      <c r="AS42" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ42" t="inlineStr">
+      <c r="AT42" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS42" t="inlineStr">
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT42" t="inlineStr">
+      <c r="AW42" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -5814,55 +5952,58 @@
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr">
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP43" t="inlineStr">
+      <c r="AS43" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ43" t="inlineStr">
+      <c r="AT43" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr">
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT43" t="inlineStr">
+      <c r="AW43" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -5930,18 +6071,18 @@
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
@@ -5949,32 +6090,35 @@
       <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="inlineStr">
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP44" t="inlineStr">
+      <c r="AS44" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ44" t="inlineStr">
+      <c r="AT44" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr">
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT44" t="inlineStr">
+      <c r="AW44" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -6050,59 +6194,62 @@
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr">
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr">
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP45" t="inlineStr">
+      <c r="AS45" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ45" t="inlineStr">
+      <c r="AT45" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr">
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT45" t="inlineStr">
+      <c r="AW45" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -6178,59 +6325,62 @@
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr">
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr">
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP46" t="inlineStr">
+      <c r="AS46" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ46" t="inlineStr">
+      <c r="AT46" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT46" t="inlineStr">
+      <c r="AW46" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -6302,55 +6452,58 @@
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr">
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP47" t="inlineStr">
+      <c r="AS47" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ47" t="inlineStr">
+      <c r="AT47" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr">
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT47" t="inlineStr">
+      <c r="AW47" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -6418,18 +6571,18 @@
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
@@ -6437,32 +6590,35 @@
       <c r="AL48" t="inlineStr"/>
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr">
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP48" t="inlineStr">
+      <c r="AS48" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ48" t="inlineStr">
+      <c r="AT48" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT48" t="inlineStr">
+      <c r="AW48" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -6538,59 +6694,62 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr">
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr">
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP49" t="inlineStr">
+      <c r="AS49" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ49" t="inlineStr">
+      <c r="AT49" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT49" t="inlineStr">
+      <c r="AW49" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -6658,18 +6817,18 @@
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
@@ -6677,32 +6836,35 @@
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
-      <c r="AO50" t="inlineStr">
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP50" t="inlineStr">
+      <c r="AS50" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ50" t="inlineStr">
+      <c r="AT50" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT50" t="inlineStr">
+      <c r="AW50" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -6778,59 +6940,62 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr">
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr">
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP51" t="inlineStr">
+      <c r="AS51" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ51" t="inlineStr">
+      <c r="AT51" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT51" t="inlineStr">
+      <c r="AW51" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -6906,59 +7071,62 @@
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr">
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr">
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP52" t="inlineStr">
+      <c r="AS52" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ52" t="inlineStr">
+      <c r="AT52" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT52" t="inlineStr">
+      <c r="AW52" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -7030,59 +7198,62 @@
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr">
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr">
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP53" t="inlineStr">
+      <c r="AS53" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ53" t="inlineStr">
+      <c r="AT53" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr">
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT53" t="inlineStr">
+      <c r="AW53" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -7154,55 +7325,58 @@
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr">
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP54" t="inlineStr">
+      <c r="AS54" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ54" t="inlineStr">
+      <c r="AT54" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr">
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT54" t="inlineStr">
+      <c r="AW54" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -7278,59 +7452,62 @@
       <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr">
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr">
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP55" t="inlineStr">
+      <c r="AS55" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ55" t="inlineStr">
+      <c r="AT55" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT55" t="inlineStr">
+      <c r="AW55" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -7398,18 +7575,18 @@
       <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
@@ -7417,32 +7594,35 @@
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="inlineStr"/>
       <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr">
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP56" t="inlineStr">
+      <c r="AS56" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ56" t="inlineStr">
+      <c r="AT56" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT56" t="inlineStr">
+      <c r="AW56" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office [registration status] SEC IAPD registration (CRD 307858) is currently inactive/withdrawn (verified via IAPD firm search, 2026-07-28); the firm is independently evidenced as operating via a recent SEC Form 13F filing (period 2024-09-30). (A withdrawn SEC registration is common for family offices exempt under the SEC Family Office Rule.)</t>
         </is>
@@ -7518,59 +7698,62 @@
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE57" t="inlineStr">
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr">
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr">
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP57" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ57" t="inlineStr">
+      <c r="AT57" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT57" t="inlineStr">
+      <c r="AW57" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -7638,18 +7821,18 @@
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE58" t="inlineStr">
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
@@ -7657,32 +7840,35 @@
       <c r="AL58" t="inlineStr"/>
       <c r="AM58" t="inlineStr"/>
       <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr">
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP58" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ58" t="inlineStr">
+      <c r="AT58" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT58" t="inlineStr">
+      <c r="AW58" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -7758,59 +7944,62 @@
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr">
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr">
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP59" t="inlineStr">
+      <c r="AS59" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ59" t="inlineStr">
+      <c r="AT59" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr">
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT59" t="inlineStr">
+      <c r="AW59" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -7878,18 +8067,18 @@
       <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
@@ -7897,32 +8086,35 @@
       <c r="AL60" t="inlineStr"/>
       <c r="AM60" t="inlineStr"/>
       <c r="AN60" t="inlineStr"/>
-      <c r="AO60" t="inlineStr">
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP60" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ60" t="inlineStr">
+      <c r="AT60" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV60" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT60" t="inlineStr">
+      <c r="AW60" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -7994,55 +8186,58 @@
       <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="inlineStr">
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP61" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ61" t="inlineStr">
+      <c r="AT61" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS61" t="inlineStr">
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT61" t="inlineStr">
+      <c r="AW61" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -8110,18 +8305,18 @@
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
@@ -8129,32 +8324,35 @@
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
-      <c r="AO62" t="inlineStr">
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings)</t>
         </is>
       </c>
-      <c r="AP62" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>SEC EDGAR (13F / SC / Form D filings) (13F holdings, aggregate 13(f) value, signatory)</t>
         </is>
       </c>
-      <c r="AQ62" t="inlineStr">
+      <c r="AT62" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT62" t="inlineStr">
+      <c r="AW62" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -8230,59 +8428,62 @@
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr">
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr"/>
-      <c r="AO63" t="inlineStr">
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP63" t="inlineStr">
+      <c r="AS63" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ63" t="inlineStr">
+      <c r="AT63" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr">
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT63" t="inlineStr">
+      <c r="AW63" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -8358,59 +8559,62 @@
       <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr"/>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE64" t="inlineStr">
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr">
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr"/>
-      <c r="AO64" t="inlineStr">
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP64" t="inlineStr">
+      <c r="AS64" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ64" t="inlineStr">
+      <c r="AT64" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS64" t="inlineStr">
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT64" t="inlineStr">
+      <c r="AW64" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -8482,59 +8686,62 @@
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr">
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr"/>
-      <c r="AO65" t="inlineStr">
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP65" t="inlineStr">
+      <c r="AS65" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ65" t="inlineStr">
+      <c r="AT65" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr">
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT65" t="inlineStr">
+      <c r="AW65" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -8610,59 +8817,62 @@
       <c r="AA66" t="inlineStr"/>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr"/>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr">
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr"/>
-      <c r="AO66" t="inlineStr">
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP66" t="inlineStr">
+      <c r="AS66" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ66" t="inlineStr">
+      <c r="AT66" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT66" t="inlineStr">
+      <c r="AW66" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -8730,55 +8940,58 @@
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="inlineStr"/>
-      <c r="AL67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM67" t="inlineStr"/>
       <c r="AN67" t="inlineStr"/>
-      <c r="AO67" t="inlineStr">
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP67" t="inlineStr">
+      <c r="AS67" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ67" t="inlineStr">
+      <c r="AT67" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT67" t="inlineStr">
+      <c r="AW67" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -8854,59 +9067,62 @@
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr"/>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE68" t="inlineStr">
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI68" t="inlineStr"/>
       <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="inlineStr"/>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="inlineStr">
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr"/>
-      <c r="AO68" t="inlineStr">
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP68" t="inlineStr">
+      <c r="AS68" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ68" t="inlineStr">
+      <c r="AT68" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT68" t="inlineStr">
+      <c r="AW68" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -8982,59 +9198,62 @@
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="inlineStr"/>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="inlineStr">
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr"/>
-      <c r="AO69" t="inlineStr">
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP69" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address); Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ69" t="inlineStr">
+      <c r="AT69" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS69" t="inlineStr">
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT69" t="inlineStr">
+      <c r="AW69" t="inlineStr">
         <is>
           <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
         </is>
@@ -9102,55 +9321,58 @@
       <c r="AA70" t="inlineStr"/>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr"/>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI70" t="inlineStr"/>
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM70" t="inlineStr"/>
       <c r="AN70" t="inlineStr"/>
-      <c r="AO70" t="inlineStr">
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
         </is>
       </c>
-      <c r="AP70" t="inlineStr">
+      <c r="AS70" t="inlineStr">
         <is>
           <t>SEC IAPD / Form ADV (investment-adviser registration) (family-office registration, firm identity &amp; office address)</t>
         </is>
       </c>
-      <c r="AQ70" t="inlineStr">
+      <c r="AT70" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
         <is>
           <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
         </is>
       </c>
-      <c r="AT70" t="inlineStr">
+      <c r="AW70" t="inlineStr">
         <is>
           <t>[same-source: single authoritative source] verified via the firm's own SEC Form 13F filing, which both surfaced and documents it; no independent free-tier second source (IAPD registration / firm website) is available for this firm, so cross-verification is limited â€” disclosed, not fabricated.</t>
         </is>
@@ -9222,59 +9444,62 @@
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr"/>
-      <c r="AD71" t="inlineStr">
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE71" t="inlineStr">
+      <c r="AG71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF71" t="inlineStr">
+      <c r="AH71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG71" t="inlineStr"/>
-      <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI71" t="inlineStr"/>
       <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="inlineStr"/>
-      <c r="AL71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM71" t="inlineStr"/>
       <c r="AN71" t="inlineStr"/>
-      <c r="AO71" t="inlineStr">
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP71" t="inlineStr">
+      <c r="AS71" t="inlineStr">
         <is>
           <t>Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ71" t="inlineStr">
+      <c r="AT71" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr">
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT71" t="inlineStr">
+      <c r="AW71" t="inlineStr">
         <is>
           <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
         </is>
@@ -9342,55 +9567,58 @@
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr"/>
-      <c r="AD72" t="inlineStr">
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE72" t="inlineStr">
+      <c r="AG72" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI72" t="inlineStr"/>
       <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="inlineStr"/>
-      <c r="AL72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM72" t="inlineStr"/>
       <c r="AN72" t="inlineStr"/>
-      <c r="AO72" t="inlineStr">
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP72" t="inlineStr">
+      <c r="AS72" t="inlineStr">
         <is>
           <t>Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ72" t="inlineStr">
+      <c r="AT72" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone; principal_name; principal_title</t>
         </is>
       </c>
-      <c r="AT72" t="inlineStr">
+      <c r="AW72" t="inlineStr">
         <is>
           <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Controlled by the Kirk Kristiansen family; no individual decision-maker is named on the site, so the principal is left could_not_verify. The firm also appears in SEC EDGAR full-text filings (Schedule 13D/13G on US holdings), corroborating its investing activity.</t>
         </is>
@@ -9466,63 +9694,66 @@
       <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr"/>
-      <c r="AD73" t="inlineStr">
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE73" t="inlineStr">
+      <c r="AG73" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AF73" t="inlineStr">
+      <c r="AH73" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG73" t="inlineStr"/>
-      <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI73" t="inlineStr"/>
       <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="inlineStr"/>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="inlineStr">
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr"/>
-      <c r="AO73" t="inlineStr">
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP73" t="inlineStr">
+      <c r="AS73" t="inlineStr">
         <is>
           <t>Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ73" t="inlineStr">
+      <c r="AT73" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT73" t="inlineStr">
+      <c r="AW73" t="inlineStr">
         <is>
           <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Self-describes as a single-family office; a smaller, public-equity focused firm â€” held at Low confidence pending a second authoritative source. Classification corrected Single-Family Office -&gt; Undetermined on 2026-07-28 after re-verifying single-vs-multi against the firm's own website; the prior label over-relied on generic 'single-family language' detection.</t>
         </is>
@@ -9590,59 +9821,62 @@
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr"/>
-      <c r="AD74" t="inlineStr">
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE74" t="inlineStr">
+      <c r="AG74" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI74" t="inlineStr"/>
       <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="inlineStr"/>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="inlineStr">
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr"/>
-      <c r="AO74" t="inlineStr">
+      <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP74" t="inlineStr">
+      <c r="AS74" t="inlineStr">
         <is>
           <t>Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ74" t="inlineStr">
+      <c r="AT74" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr">
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone; principal_name; principal_title</t>
         </is>
       </c>
-      <c r="AT74" t="inlineStr">
+      <c r="AW74" t="inlineStr">
         <is>
           <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Controlled by the Colruyt family; no individual decision-maker is named on the site, so the principal is left could_not_verify.</t>
         </is>
@@ -9718,59 +9952,62 @@
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr"/>
-      <c r="AD75" t="inlineStr">
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE75" t="inlineStr">
+      <c r="AG75" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF75" t="inlineStr">
+      <c r="AH75" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AG75" t="inlineStr"/>
-      <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI75" t="inlineStr"/>
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="inlineStr"/>
-      <c r="AL75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM75" t="inlineStr"/>
       <c r="AN75" t="inlineStr"/>
-      <c r="AO75" t="inlineStr">
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP75" t="inlineStr">
+      <c r="AS75" t="inlineStr">
         <is>
           <t>Firm Website (family-office status/type, description, principal)</t>
         </is>
       </c>
-      <c r="AQ75" t="inlineStr">
+      <c r="AT75" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT75" t="inlineStr">
+      <c r="AW75" t="inlineStr">
         <is>
           <t>Discovered via a non-SEC lens (Wikipedia/Wikidata Category:Family_offices); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The firm also appears in SEC EDGAR full-text filings on US holdings, corroborating its investing activity.</t>
         </is>
@@ -9846,59 +10083,62 @@
       <c r="AA76" t="inlineStr"/>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr"/>
-      <c r="AD76" t="inlineStr">
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE76" t="inlineStr">
+      <c r="AG76" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI76" t="inlineStr"/>
       <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="inlineStr">
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr"/>
-      <c r="AO76" t="inlineStr">
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP76" t="inlineStr">
+      <c r="AS76" t="inlineStr">
         <is>
           <t>Firm Website (single-family-office status, firm identity)</t>
         </is>
       </c>
-      <c r="AQ76" t="inlineStr">
+      <c r="AT76" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR76" t="inlineStr">
+      <c r="AU76" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AS76" t="inlineStr">
+      <c r="AV76" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT76" t="inlineStr">
+      <c r="AW76" t="inlineStr">
         <is>
           <t>Discovered via the curated/notable-reference lens (Wikipedia's family-office listings); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The family the office serves is named in the classification evidence; it is deliberately NOT recorded as the office's principal, because the site does not name the office's own decision-maker. Wikipedia's family-office category lists this firm under its later corporate name (DFO Management, LLC); the firm's own site presents as MSD Capital, L.P., and the record uses the site's own name â€” identity verified against that site.</t>
         </is>
@@ -9974,59 +10214,62 @@
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr"/>
-      <c r="AD77" t="inlineStr">
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE77" t="inlineStr">
+      <c r="AG77" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF77" t="inlineStr"/>
-      <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="inlineStr">
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr"/>
-      <c r="AO77" t="inlineStr">
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP77" t="inlineStr">
+      <c r="AS77" t="inlineStr">
         <is>
           <t>Firm Website (single-family-office status, firm identity)</t>
         </is>
       </c>
-      <c r="AQ77" t="inlineStr">
+      <c r="AT77" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR77" t="inlineStr">
+      <c r="AU77" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AS77" t="inlineStr">
+      <c r="AV77" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT77" t="inlineStr">
+      <c r="AW77" t="inlineStr">
         <is>
           <t>Discovered via the curated/notable-reference lens (Wikipedia's family-office listings); classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. The family the office serves is named in the classification evidence; it is deliberately NOT recorded as the office's principal, because the site does not name the office's own decision-maker.</t>
         </is>
@@ -10086,55 +10329,58 @@
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr">
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE78" t="inlineStr">
+      <c r="AG78" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI78" t="inlineStr"/>
       <c r="AJ78" t="inlineStr"/>
       <c r="AK78" t="inlineStr"/>
-      <c r="AL78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="AM78" t="inlineStr"/>
       <c r="AN78" t="inlineStr"/>
-      <c r="AO78" t="inlineStr">
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP78" t="inlineStr">
+      <c r="AS78" t="inlineStr">
         <is>
           <t>Firm Website (single-family-office status, firm identity)</t>
         </is>
       </c>
-      <c r="AQ78" t="inlineStr">
+      <c r="AT78" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR78" t="inlineStr">
+      <c r="AU78" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr">
+      <c r="AV78" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT78" t="inlineStr">
+      <c r="AW78" t="inlineStr">
         <is>
           <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
         </is>
@@ -10198,59 +10444,62 @@
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr"/>
-      <c r="AD79" t="inlineStr">
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE79" t="inlineStr">
+      <c r="AG79" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI79" t="inlineStr"/>
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr"/>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr">
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr"/>
-      <c r="AO79" t="inlineStr">
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP79" t="inlineStr">
+      <c r="AS79" t="inlineStr">
         <is>
           <t>Firm Website (single-family-office status, firm identity)</t>
         </is>
       </c>
-      <c r="AQ79" t="inlineStr">
+      <c r="AT79" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR79" t="inlineStr">
+      <c r="AU79" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AS79" t="inlineStr">
+      <c r="AV79" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT79" t="inlineStr">
+      <c r="AW79" t="inlineStr">
         <is>
           <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify.</t>
         </is>
@@ -10318,59 +10567,62 @@
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr">
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE80" t="inlineStr">
+      <c r="AG80" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="inlineStr"/>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr">
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr"/>
-      <c r="AO80" t="inlineStr">
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP80" t="inlineStr">
+      <c r="AS80" t="inlineStr">
         <is>
           <t>Firm Website (single-family-office status, firm identity)</t>
         </is>
       </c>
-      <c r="AQ80" t="inlineStr">
+      <c r="AT80" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR80" t="inlineStr">
+      <c r="AU80" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AS80" t="inlineStr">
+      <c r="AV80" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT80" t="inlineStr">
+      <c r="AW80" t="inlineStr">
         <is>
           <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Accepted on human review: the automated judge (on a fallback model) missed the site's verbatim opening line, whose construction is identical to the accepted Korys evidence ('the ... investment company of the &lt;family&gt; family'); the overrule and its basis are recorded here for auditability. The site states the firm is French (groupe ArtÃ©mis); city is not stated and is left blank.</t>
         </is>
@@ -10434,59 +10686,62 @@
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr"/>
-      <c r="AD81" t="inlineStr">
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AE81" t="inlineStr">
+      <c r="AG81" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr"/>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr">
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr"/>
-      <c r="AO81" t="inlineStr">
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr">
         <is>
           <t>Curated directory / reference (Wikipedia, associations)</t>
         </is>
       </c>
-      <c r="AP81" t="inlineStr">
+      <c r="AS81" t="inlineStr">
         <is>
           <t>Firm Website (single-family-office status, firm identity)</t>
         </is>
       </c>
-      <c r="AQ81" t="inlineStr">
+      <c r="AT81" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="AR81" t="inlineStr">
+      <c r="AU81" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="AS81" t="inlineStr">
+      <c r="AV81" t="inlineStr">
         <is>
           <t>estimated_aum; corporate_linkedin; principal_name; principal_title; principal_linkedin; principal_email; principal_phone; hq_phone</t>
         </is>
       </c>
-      <c r="AT81" t="inlineStr">
+      <c r="AW81" t="inlineStr">
         <is>
           <t>Discovered via the curated/notable-reference lens; classification and firm identity verified against the firm's own authoritative website (single verification source). AUM and individual contact details are not available from free authoritative sources and are left could_not_verify. Perelman is the owner; the site names no separate office decision-maker, so principal fields stay blank. Geography is not stated on the scraped pages and is left blank.</t>
         </is>
@@ -34307,7 +34562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34486,7 +34741,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Decision-maker contact; blank + could_not_verify when not verifiable.</t>
+          <t>A route to the NAMED principal specifically — 13F/ADV signatory phone, or a firm team/about page that name-matches an email/LinkedIn to that person. Blank + could_not_verify when no such evidence exists.</t>
         </is>
       </c>
     </row>
@@ -34505,94 +34760,118 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>recent_signal_1..3 (+ _date, _source)</t>
+          <t>firm_contact_email</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Recent, dated activity. This build: SEC Form 13F portfolio changes (new positions vs the prior quarter), sourced to EDGAR; news/hire signals were not available on free tiers (GDELT rate-limited to zero).</t>
+          <t>The firm's own published outreach inbox (e.g. info@) — a real, sourced channel, but explicitly NOT a route to any named individual. Distinct from principal_email.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>*_confidence</t>
+          <t>firm_contact_email_status</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Per-field confidence, derived from the cell's evidence (never inflated).</t>
+          <t>deliverable / risky / could_not_verify for firm_contact_email.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>discovery_source</t>
+          <t>recent_signal_1..3 (+ _date, _source)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>How the firm was FOUND (discovery ≠ verification).</t>
+          <t>Recent, dated activity. This build: SEC Form 13F portfolio changes (new positions vs the prior quarter), sourced to EDGAR; news/hire signals were not available on free tiers (GDELT rate-limited to zero).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>verification_sources</t>
+          <t>*_confidence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Independent authoritative sources used to PROVE facts.</t>
+          <t>Per-field confidence, derived from the cell's evidence (never inflated).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>record_confidence</t>
+          <t>discovery_source</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Overall confidence — the weakest link across identity anchors.</t>
+          <t>How the firm was FOUND (discovery ≠ verification).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>data_as_of</t>
+          <t>verification_sources</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Date the record was validated.</t>
+          <t>Independent authoritative sources used to PROVE facts.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>could_not_verify</t>
+          <t>record_confidence</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fields honestly left blank because they could not be verified.</t>
+          <t>Overall confidence — the weakest link across identity anchors.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>data_as_of</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Date the record was validated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>could_not_verify</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fields honestly left blank because they could not be verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>reviewer_notes</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Human judgment notes (e.g. same-source justification).</t>
         </is>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW176"/>
+  <dimension ref="A1:AW183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33669,6 +33669,1325 @@
       <c r="AW176" t="inlineStr">
         <is>
           <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>fo_e9da1e4e46</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PENTA FAMILY OFFICE SA</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: multi-family language</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>​The pentagram represents the 5 members of the founder’s family, illustrating the importance of family values for the firm</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v/>
+      </c>
+      <c r="G177" t="n">
+        <v/>
+      </c>
+      <c r="H177" t="n">
+        <v/>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>https://www.penta-ph.com/en/</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v/>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>GENEVA</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v/>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v/>
+      </c>
+      <c r="O177" t="n">
+        <v/>
+      </c>
+      <c r="P177" t="n">
+        <v/>
+      </c>
+      <c r="Q177" t="n">
+        <v/>
+      </c>
+      <c r="R177" t="n">
+        <v/>
+      </c>
+      <c r="S177" t="n">
+        <v/>
+      </c>
+      <c r="T177" t="n">
+        <v/>
+      </c>
+      <c r="U177" t="n">
+        <v/>
+      </c>
+      <c r="V177" t="n">
+        <v/>
+      </c>
+      <c r="W177" t="n">
+        <v/>
+      </c>
+      <c r="X177" t="n">
+        <v/>
+      </c>
+      <c r="Y177" t="n">
+        <v/>
+      </c>
+      <c r="Z177" t="n">
+        <v/>
+      </c>
+      <c r="AA177" t="n">
+        <v/>
+      </c>
+      <c r="AB177" t="n">
+        <v/>
+      </c>
+      <c r="AC177" t="n">
+        <v/>
+      </c>
+      <c r="AD177" t="n">
+        <v/>
+      </c>
+      <c r="AE177" t="n">
+        <v/>
+      </c>
+      <c r="AF177" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG177" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH177" t="n">
+        <v/>
+      </c>
+      <c r="AI177" t="n">
+        <v/>
+      </c>
+      <c r="AJ177" t="n">
+        <v/>
+      </c>
+      <c r="AK177" t="n">
+        <v/>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM177" t="n">
+        <v/>
+      </c>
+      <c r="AN177" t="n">
+        <v/>
+      </c>
+      <c r="AO177" t="n">
+        <v/>
+      </c>
+      <c r="AP177" t="n">
+        <v/>
+      </c>
+      <c r="AQ177" t="n">
+        <v/>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT177" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW177" t="inlineStr">
+        <is>
+          <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>fo_9ef7b4677a</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ELYSEUM FAMILY OFFICE S.A.</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Founded in 2011, Elyseum Investment provide first-rate investment services its clients with a focus on Private Equity, Real Estate and Family Office.</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Founded in 2011, Elyseum Investment provides first-rate investment services to its clients with a focus on Private Equity, Real Estate and Family Office.</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v/>
+      </c>
+      <c r="H178" t="n">
+        <v/>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>https://www.elyseum-investment.com/</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v/>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>GENEVA</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v/>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v/>
+      </c>
+      <c r="O178" t="n">
+        <v/>
+      </c>
+      <c r="P178" t="n">
+        <v/>
+      </c>
+      <c r="Q178" t="n">
+        <v/>
+      </c>
+      <c r="R178" t="n">
+        <v/>
+      </c>
+      <c r="S178" t="n">
+        <v/>
+      </c>
+      <c r="T178" t="n">
+        <v/>
+      </c>
+      <c r="U178" t="n">
+        <v/>
+      </c>
+      <c r="V178" t="n">
+        <v/>
+      </c>
+      <c r="W178" t="n">
+        <v/>
+      </c>
+      <c r="X178" t="n">
+        <v/>
+      </c>
+      <c r="Y178" t="n">
+        <v/>
+      </c>
+      <c r="Z178" t="n">
+        <v/>
+      </c>
+      <c r="AA178" t="n">
+        <v/>
+      </c>
+      <c r="AB178" t="n">
+        <v/>
+      </c>
+      <c r="AC178" t="n">
+        <v/>
+      </c>
+      <c r="AD178" t="n">
+        <v/>
+      </c>
+      <c r="AE178" t="n">
+        <v/>
+      </c>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH178" t="n">
+        <v/>
+      </c>
+      <c r="AI178" t="n">
+        <v/>
+      </c>
+      <c r="AJ178" t="n">
+        <v/>
+      </c>
+      <c r="AK178" t="n">
+        <v/>
+      </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM178" t="n">
+        <v/>
+      </c>
+      <c r="AN178" t="n">
+        <v/>
+      </c>
+      <c r="AO178" t="n">
+        <v/>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ178" t="n">
+        <v/>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT178" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>fo_30c545d0e9</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>ALCALA MULTI FAMILY OFFICE</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: multi-family language</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Ofrecemos asesoría integral y estrategias personalizadas para asegurar el futuro financiero de tu familia.</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v/>
+      </c>
+      <c r="G179" t="n">
+        <v/>
+      </c>
+      <c r="H179" t="n">
+        <v/>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>https://www.alcala-inversiones.com/es/inicio</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v/>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>NEW YORK</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v/>
+      </c>
+      <c r="O179" t="n">
+        <v/>
+      </c>
+      <c r="P179" t="n">
+        <v/>
+      </c>
+      <c r="Q179" t="n">
+        <v/>
+      </c>
+      <c r="R179" t="n">
+        <v/>
+      </c>
+      <c r="S179" t="n">
+        <v/>
+      </c>
+      <c r="T179" t="n">
+        <v/>
+      </c>
+      <c r="U179" t="n">
+        <v/>
+      </c>
+      <c r="V179" t="n">
+        <v/>
+      </c>
+      <c r="W179" t="n">
+        <v/>
+      </c>
+      <c r="X179" t="n">
+        <v/>
+      </c>
+      <c r="Y179" t="n">
+        <v/>
+      </c>
+      <c r="Z179" t="n">
+        <v/>
+      </c>
+      <c r="AA179" t="n">
+        <v/>
+      </c>
+      <c r="AB179" t="n">
+        <v/>
+      </c>
+      <c r="AC179" t="n">
+        <v/>
+      </c>
+      <c r="AD179" t="n">
+        <v/>
+      </c>
+      <c r="AE179" t="n">
+        <v/>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH179" t="n">
+        <v/>
+      </c>
+      <c r="AI179" t="n">
+        <v/>
+      </c>
+      <c r="AJ179" t="n">
+        <v/>
+      </c>
+      <c r="AK179" t="n">
+        <v/>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM179" t="n">
+        <v/>
+      </c>
+      <c r="AN179" t="n">
+        <v/>
+      </c>
+      <c r="AO179" t="n">
+        <v/>
+      </c>
+      <c r="AP179" t="n">
+        <v/>
+      </c>
+      <c r="AQ179" t="n">
+        <v/>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT179" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>fo_79d6c6baca</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>FIFTH AVENUE FAMILY OFFICE</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Fifth Avenue Family Office is a team of talented professionals dedicated to serving a select group of entrepreneurial families. We provide family office services that coordinate, manage, and advise across the full-net-worth spectrum. Our goal is to provide our client families with enhanced peace of mind so they can confidently live their lives, love their families and leave their legacies.</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v/>
+      </c>
+      <c r="G180" t="n">
+        <v/>
+      </c>
+      <c r="H180" t="n">
+        <v/>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>https://fifthavenuefamily.com/</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v/>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>NAPLES</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v/>
+      </c>
+      <c r="O180" t="n">
+        <v/>
+      </c>
+      <c r="P180" t="n">
+        <v/>
+      </c>
+      <c r="Q180" t="n">
+        <v/>
+      </c>
+      <c r="R180" t="n">
+        <v/>
+      </c>
+      <c r="S180" t="n">
+        <v/>
+      </c>
+      <c r="T180" t="n">
+        <v/>
+      </c>
+      <c r="U180" t="n">
+        <v/>
+      </c>
+      <c r="V180" t="n">
+        <v/>
+      </c>
+      <c r="W180" t="n">
+        <v/>
+      </c>
+      <c r="X180" t="n">
+        <v/>
+      </c>
+      <c r="Y180" t="n">
+        <v/>
+      </c>
+      <c r="Z180" t="n">
+        <v/>
+      </c>
+      <c r="AA180" t="n">
+        <v/>
+      </c>
+      <c r="AB180" t="n">
+        <v/>
+      </c>
+      <c r="AC180" t="n">
+        <v/>
+      </c>
+      <c r="AD180" t="n">
+        <v/>
+      </c>
+      <c r="AE180" t="n">
+        <v/>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH180" t="n">
+        <v/>
+      </c>
+      <c r="AI180" t="n">
+        <v/>
+      </c>
+      <c r="AJ180" t="n">
+        <v/>
+      </c>
+      <c r="AK180" t="n">
+        <v/>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM180" t="n">
+        <v/>
+      </c>
+      <c r="AN180" t="n">
+        <v/>
+      </c>
+      <c r="AO180" t="n">
+        <v/>
+      </c>
+      <c r="AP180" t="n">
+        <v/>
+      </c>
+      <c r="AQ180" t="n">
+        <v/>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT180" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>fo_cf7e79b88a</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>LEGACY ROAD FAMILY OFFICES</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Preserve and grow what matters most. Legacy Road Family Offices delivers expert wealth management and financial planning for high-net-worth families and individuals.</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>The mission of Legacy Road is to provide world-class, institutional quality, investment management and family office services designed to meet the diverse needs of professional athletes, entertainers, and exceptionally affluent individuals and families.</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v/>
+      </c>
+      <c r="H181" t="n">
+        <v/>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>https://www.legacyroad.com/</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v/>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v/>
+      </c>
+      <c r="O181" t="n">
+        <v/>
+      </c>
+      <c r="P181" t="n">
+        <v/>
+      </c>
+      <c r="Q181" t="n">
+        <v/>
+      </c>
+      <c r="R181" t="n">
+        <v/>
+      </c>
+      <c r="S181" t="n">
+        <v/>
+      </c>
+      <c r="T181" t="n">
+        <v/>
+      </c>
+      <c r="U181" t="n">
+        <v/>
+      </c>
+      <c r="V181" t="n">
+        <v/>
+      </c>
+      <c r="W181" t="n">
+        <v/>
+      </c>
+      <c r="X181" t="n">
+        <v/>
+      </c>
+      <c r="Y181" t="n">
+        <v/>
+      </c>
+      <c r="Z181" t="n">
+        <v/>
+      </c>
+      <c r="AA181" t="n">
+        <v/>
+      </c>
+      <c r="AB181" t="n">
+        <v/>
+      </c>
+      <c r="AC181" t="n">
+        <v/>
+      </c>
+      <c r="AD181" t="n">
+        <v/>
+      </c>
+      <c r="AE181" t="n">
+        <v/>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH181" t="n">
+        <v/>
+      </c>
+      <c r="AI181" t="n">
+        <v/>
+      </c>
+      <c r="AJ181" t="n">
+        <v/>
+      </c>
+      <c r="AK181" t="n">
+        <v/>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM181" t="n">
+        <v/>
+      </c>
+      <c r="AN181" t="n">
+        <v/>
+      </c>
+      <c r="AO181" t="n">
+        <v/>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ181" t="n">
+        <v/>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT181" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>fo_ef3c1aeb59</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>MACI FAMILY OFFICE ADVISORS</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Maci capital family office investment advisors new york city</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>We provide comprehensive financial advice, planning, investment &amp; wealth management services to several multi-generational families whose members are spread throughout North America, Europe and Australia.</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v/>
+      </c>
+      <c r="H182" t="n">
+        <v/>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>https://www.macicapital.com/</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v/>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>NEW YORK</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v/>
+      </c>
+      <c r="O182" t="n">
+        <v/>
+      </c>
+      <c r="P182" t="n">
+        <v/>
+      </c>
+      <c r="Q182" t="n">
+        <v/>
+      </c>
+      <c r="R182" t="n">
+        <v/>
+      </c>
+      <c r="S182" t="n">
+        <v/>
+      </c>
+      <c r="T182" t="n">
+        <v/>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>joanne@macicapital.com</t>
+        </is>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W182" t="n">
+        <v/>
+      </c>
+      <c r="X182" t="n">
+        <v/>
+      </c>
+      <c r="Y182" t="n">
+        <v/>
+      </c>
+      <c r="Z182" t="n">
+        <v/>
+      </c>
+      <c r="AA182" t="n">
+        <v/>
+      </c>
+      <c r="AB182" t="n">
+        <v/>
+      </c>
+      <c r="AC182" t="n">
+        <v/>
+      </c>
+      <c r="AD182" t="n">
+        <v/>
+      </c>
+      <c r="AE182" t="n">
+        <v/>
+      </c>
+      <c r="AF182" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH182" t="n">
+        <v/>
+      </c>
+      <c r="AI182" t="n">
+        <v/>
+      </c>
+      <c r="AJ182" t="n">
+        <v/>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM182" t="n">
+        <v/>
+      </c>
+      <c r="AN182" t="n">
+        <v/>
+      </c>
+      <c r="AO182" t="n">
+        <v/>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ182" t="n">
+        <v/>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT182" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>fo_1ed11ef389</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>QP GLOBAL FAMILY OFFICES, LLC</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single-family language</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Elite single-family office management: Full ownership and control for discerning families. We handle design, leadership, staffing, operations, investments, and governance—so you focus on legacy and life.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Our shared model means: You own everything — your wealth, your vision, your decisions, your legacy.</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v/>
+      </c>
+      <c r="H183" t="n">
+        <v/>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>https://www.qp-global.com/</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v/>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>GREENWICH</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v/>
+      </c>
+      <c r="O183" t="n">
+        <v/>
+      </c>
+      <c r="P183" t="n">
+        <v/>
+      </c>
+      <c r="Q183" t="n">
+        <v/>
+      </c>
+      <c r="R183" t="n">
+        <v/>
+      </c>
+      <c r="S183" t="n">
+        <v/>
+      </c>
+      <c r="T183" t="n">
+        <v/>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>info@qp-global.com</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W183" t="n">
+        <v/>
+      </c>
+      <c r="X183" t="n">
+        <v/>
+      </c>
+      <c r="Y183" t="n">
+        <v/>
+      </c>
+      <c r="Z183" t="n">
+        <v/>
+      </c>
+      <c r="AA183" t="n">
+        <v/>
+      </c>
+      <c r="AB183" t="n">
+        <v/>
+      </c>
+      <c r="AC183" t="n">
+        <v/>
+      </c>
+      <c r="AD183" t="n">
+        <v/>
+      </c>
+      <c r="AE183" t="n">
+        <v/>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH183" t="n">
+        <v/>
+      </c>
+      <c r="AI183" t="n">
+        <v/>
+      </c>
+      <c r="AJ183" t="n">
+        <v/>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM183" t="n">
+        <v/>
+      </c>
+      <c r="AN183" t="n">
+        <v/>
+      </c>
+      <c r="AO183" t="n">
+        <v/>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ183" t="n">
+        <v/>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT183" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>same-source: discovered via SEC 13F full-text search on filings; verified via the distinct SEC submissions registration record and the firm's regulatory self-identification as a family office | firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
         </is>
       </c>
     </row>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW195"/>
+  <dimension ref="A1:AW197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23281,6 +23281,285 @@
       </c>
       <c r="AW195" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>fo_9740c3127a</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>every Family Office</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Not true Consistently true 1 2 3 4 5 6 11 Personal development and legacy planning are integrated into long-term strategy.</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>https://www.everyfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>ROSWELL</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr"/>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="inlineStr"/>
+      <c r="AB196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
+      <c r="AE196" t="inlineStr"/>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr"/>
+      <c r="AJ196" t="inlineStr"/>
+      <c r="AK196" t="inlineStr"/>
+      <c r="AL196" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr"/>
+      <c r="AN196" t="inlineStr"/>
+      <c r="AO196" t="inlineStr"/>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr"/>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>Web search (EXA)</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT196" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>DCA Family Office</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Investment, Family and Legacy Solutions
+for Successful Multi-Generational Families</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>$138M total regulatory AUM (SEC Form ADV Item 5.F as of 2023)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>https://dcafamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>ROSEVILLE</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Jennifer Rocca</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Trustee</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>info@dcafamilyoffice.com</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr"/>
+      <c r="X197" t="inlineStr"/>
+      <c r="Y197" t="inlineStr"/>
+      <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="inlineStr"/>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
+      <c r="AE197" t="inlineStr"/>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr"/>
+      <c r="AJ197" t="inlineStr"/>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr"/>
+      <c r="AN197" t="inlineStr"/>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr"/>
+      <c r="AQ197" t="inlineStr"/>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>Web search (Tavily)</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type); SEC IAPD / Form ADV (investment-adviser registration) (total regulatory AUM (ADV Item 5.F), owner/control person (ADV Schedule A))</t>
+        </is>
+      </c>
+      <c r="AT197" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm | firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23292,7 +23571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H445"/>
+  <dimension ref="A1:H457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40208,6 +40487,462 @@
         </is>
       </c>
       <c r="H445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>fo_9740c3127a</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>https://www.everyfamilyoffice.com</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>fo_9740c3127a</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/104605</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>fo_9740c3127a</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>https://www.everyfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>fo_9740c3127a</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>https://www.everyfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>https://dcafamilyoffice.com</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://dcafamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>https://dcafamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>https://dcafamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>estimated_aum</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>principal_name</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>principal_title</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40220,7 +40955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F487"/>
+  <dimension ref="A1:F494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53666,6 +54401,214 @@
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>fo_9740c3127a</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/104605</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>fo_9740c3127a</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>https://www.everyfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>fo_9740c3127a</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Web search (EXA)</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>https://dcafamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>total regulatory AUM (ADV Item 5.F), owner/control person (ADV Schedule A)</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/322047</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>fo_11fec2354c</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Web search (Tavily)</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr"/>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW197"/>
+  <dimension ref="A1:AW202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23560,6 +23560,650 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Tiedemann Advisors</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AlTi Global is a leading independent UHNW wealth manager. We align capital with purpose for families, foundations, and institutions across borders and generations.</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>We align capital with goals and values to create outcomes that matter.</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>https://alti-global.com/</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>NEW YORK</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr"/>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+      <c r="AE198" t="inlineStr"/>
+      <c r="AF198" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG198" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr"/>
+      <c r="AJ198" t="inlineStr"/>
+      <c r="AK198" t="inlineStr"/>
+      <c r="AL198" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM198" t="inlineStr"/>
+      <c r="AN198" t="inlineStr"/>
+      <c r="AO198" t="inlineStr"/>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr"/>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT198" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>fo_206d0b3ece</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Adamo Capital</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Family investing with an endowment approach Health is wealth.</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>https://adamo.capital/</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="inlineStr"/>
+      <c r="Z199" t="inlineStr"/>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+      <c r="AE199" t="inlineStr"/>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr"/>
+      <c r="AJ199" t="inlineStr"/>
+      <c r="AK199" t="inlineStr"/>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr"/>
+      <c r="AN199" t="inlineStr"/>
+      <c r="AO199" t="inlineStr"/>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr"/>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT199" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>BigSur Partners</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: multi-family language</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>BigSur Partners was founded at the request of its five anchor families, who approached the firm's founders looking for a better way to be served.
+BigSur provides clients with a family office approach, a relationship founded upon unbiased advice, transparency, full customization and constant communication.</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>​ We are process driven and highly disciplined in our approach, similar to how large endowments, foundations and other institutions invest and preserve generational wealth.</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>https://www.bigsurpartners.com/</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>info@bigsurpartners.com</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr"/>
+      <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
+      <c r="AE200" t="inlineStr"/>
+      <c r="AF200" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG200" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr"/>
+      <c r="AJ200" t="inlineStr"/>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL200" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM200" t="inlineStr"/>
+      <c r="AN200" t="inlineStr"/>
+      <c r="AO200" t="inlineStr"/>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr"/>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT200" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Klosters Capital</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: multi-family language</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Gestión de Patrimonios con un enfoque de Multi Family Office Contáctanos Gestión de Patrimonios con un enfoque de Multi Family Office Contáctanos Gestión de Patrimonios con un enfoque de Multi Family Office Contáctanos Gestión de Patrimonios con un enfoque de Multi Family Office Contáctanos Sobre Nosotros Soluciones para tus objetivos financieros Klosters Capital España permite […]</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>https://klosters-capital.es/</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>info@klosters-capital.es</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr"/>
+      <c r="X201" t="inlineStr"/>
+      <c r="Y201" t="inlineStr"/>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
+      <c r="AE201" t="inlineStr"/>
+      <c r="AF201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr"/>
+      <c r="AJ201" t="inlineStr"/>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM201" t="inlineStr"/>
+      <c r="AN201" t="inlineStr"/>
+      <c r="AO201" t="inlineStr"/>
+      <c r="AP201" t="inlineStr"/>
+      <c r="AQ201" t="inlineStr"/>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS201" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT201" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV201" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>fo_7bdf1a2e53</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Larch Capital Partners</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: multi-family language</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>https://www.larchcapitalpartners.com/</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="inlineStr"/>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
+      <c r="AE202" t="inlineStr"/>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr"/>
+      <c r="AJ202" t="inlineStr"/>
+      <c r="AK202" t="inlineStr"/>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr"/>
+      <c r="AN202" t="inlineStr"/>
+      <c r="AO202" t="inlineStr"/>
+      <c r="AP202" t="inlineStr"/>
+      <c r="AQ202" t="inlineStr"/>
+      <c r="AR202" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT202" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23571,7 +24215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H457"/>
+  <dimension ref="A1:H480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40943,6 +41587,880 @@
         </is>
       </c>
       <c r="H457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>https://alti-global.com</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/147189</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>https://alti-global.com/</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>https://alti-global.com/</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>https://alti-global.com/</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>fo_206d0b3ece</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>https://adamo.capital</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>fo_206d0b3ece</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/315653</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>fo_206d0b3ece</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>https://adamo.capital/</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>fo_206d0b3ece</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>https://adamo.capital/</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>https://www.bigsurpartners.com</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/146511</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>https://www.bigsurpartners.com/</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>https://www.bigsurpartners.com/</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>https://www.bigsurpartners.com/</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>https://www.bigsurpartners.com/</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>https://klosters-capital.es</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/285582</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>https://klosters-capital.es/</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>https://klosters-capital.es/</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>https://klosters-capital.es/</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>fo_7bdf1a2e53</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>https://www.larchcapitalpartners.com</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>fo_7bdf1a2e53</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/307653</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>fo_7bdf1a2e53</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>https://www.larchcapitalpartners.com/</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40955,7 +42473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F494"/>
+  <dimension ref="A1:F509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54609,6 +56127,446 @@
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/147189</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>https://alti-global.com/</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>fo_c1bb45e829</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>fo_206d0b3ece</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/315653</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>fo_206d0b3ece</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>https://adamo.capital/</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>fo_206d0b3ece</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr"/>
+      <c r="E500" t="inlineStr"/>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/146511</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>https://www.bigsurpartners.com/</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>fo_88bb20d196</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/285582</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>https://klosters-capital.es/</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>fo_5b6b067658</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>fo_7bdf1a2e53</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/307653</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>fo_7bdf1a2e53</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>https://www.larchcapitalpartners.com/</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>fo_7bdf1a2e53</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
+      <c r="E509" t="inlineStr"/>
+      <c r="F509" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>

--- a/data/final/family_offices.xlsx
+++ b/data/final/family_offices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW202"/>
+  <dimension ref="A1:AW219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24204,6 +24204,2297 @@
       </c>
       <c r="AW202" t="inlineStr"/>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>fo_e9e4e52a58</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Mary Oppenheimer Daughters (MODO)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single-family language</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Located in Johannesburg, London, and the Isle of Man, MODO stewards a portfolio of business investments and philanthropic programmes rooted in the family’s long-standing commitment to social progress and principled, inclusive values.</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>https://oppenheimer-daughters.com/</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr"/>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+      <c r="AE203" t="inlineStr"/>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr"/>
+      <c r="AJ203" t="inlineStr"/>
+      <c r="AK203" t="inlineStr"/>
+      <c r="AL203" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr"/>
+      <c r="AN203" t="inlineStr"/>
+      <c r="AO203" t="inlineStr"/>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr"/>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT203" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Othongathi Investments</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Othongathi Investments is a trusted investment company South Africa businesses rely on for strategic growth, financial solutions and long-term value creation.</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>As an experienced investment company South African businesses trust, we focus on delivering sustainable growth and long-term value.</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>https://tginvest.co.za/</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>info@tginvest.co.za</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr"/>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="inlineStr"/>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
+      <c r="AE204" t="inlineStr"/>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr"/>
+      <c r="AI204" t="inlineStr"/>
+      <c r="AJ204" t="inlineStr"/>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL204" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr"/>
+      <c r="AN204" t="inlineStr"/>
+      <c r="AO204" t="inlineStr"/>
+      <c r="AP204" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr"/>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT204" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU204" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV204" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>fo_f3583bbbe4</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Nderezina Family Office (Pty) Ltd, trading as Lucratus</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>The goal of the Nyoni wealth fund is to create long-term wealth for the Nderezina Family to gain higher returns than what the bank provides for their dormant capital to preserve wealth.</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>https://lucratus.co.za/</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Durban</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>fund.manager@lucratus.co.za</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
+      <c r="AE205" t="inlineStr"/>
+      <c r="AF205" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG205" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH205" t="inlineStr"/>
+      <c r="AI205" t="inlineStr"/>
+      <c r="AJ205" t="inlineStr"/>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL205" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM205" t="inlineStr"/>
+      <c r="AN205" t="inlineStr"/>
+      <c r="AO205" t="inlineStr"/>
+      <c r="AP205" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr"/>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT205" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Bay Capital Family Office</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: multi-family language</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Bay Capital is a multi-family office founded to help our selected client families seize the opportunities of wealth and avoid the pitfalls. Our founding family office clients envisioned a firm offering independent, tailored investment advice with transparent communication and genuine care. They provided the vision, and we brought it to life. Our Core Values Family […]</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Our Core Values Family Focus We are passionate about working with families to invest intentionally, simplify the complexities of wealth, and cultivate a culture that fosters trust, communication, and lasting legacies.</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>$887M total regulatory AUM (SEC Form ADV Item 5.F as of 2024)</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>https://baycapital.co.za/</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>NEW YORK</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Michael David Nelson</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer And Chief Investment Officer</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>invest@baycapital.co.za</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr"/>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
+      <c r="AD206" t="inlineStr"/>
+      <c r="AE206" t="inlineStr"/>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr"/>
+      <c r="AJ206" t="inlineStr"/>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL206" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr"/>
+      <c r="AN206" t="inlineStr"/>
+      <c r="AO206" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AP206" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr"/>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type); SEC IAPD / Form ADV (investment-adviser registration) (total regulatory AUM (ADV Item 5.F), owner/control person (ADV Schedule A))</t>
+        </is>
+      </c>
+      <c r="AT206" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU206" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV206" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_phone</t>
+        </is>
+      </c>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>estimated_aum is TOTAL regulatory AUM (SEC Form ADV Item 5.F); principal is a Form ADV Schedule A control person — an owner / executive officer of the firm | firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Garde Capital</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: multi-family language</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Garde Capital offers holistic solutions to families and corporates on estate planning, corporate structuring and trust administration.</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Garde Capital is a boutique multi-family office management firm based in Stellenbosch, South Africa.</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>https://gardecapital.co.za/wp/</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>SEATTLE</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>shaun@gardecapital.co.za</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
+      <c r="AD207" t="inlineStr"/>
+      <c r="AE207" t="inlineStr"/>
+      <c r="AF207" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH207" t="inlineStr"/>
+      <c r="AI207" t="inlineStr"/>
+      <c r="AJ207" t="inlineStr"/>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL207" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr"/>
+      <c r="AN207" t="inlineStr"/>
+      <c r="AO207" t="inlineStr"/>
+      <c r="AP207" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ207" t="inlineStr"/>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS207" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT207" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV207" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Schmidt Family Office (SFO)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Multi-Family Office</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: multi-family language</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>SFO is a multi-family office headquartered in Stellenbosch. We serve as wealth managers to leading multi-generational families.</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>We serve as wealth managers to leading multi-generational families.</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>https://www.sfo.co.za/</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>info@sfo.co.za</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
+      <c r="AE208" t="inlineStr"/>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr"/>
+      <c r="AI208" t="inlineStr"/>
+      <c r="AJ208" t="inlineStr"/>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL208" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr"/>
+      <c r="AN208" t="inlineStr"/>
+      <c r="AO208" t="inlineStr"/>
+      <c r="AP208" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ208" t="inlineStr"/>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT208" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV208" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>fo_9cd2efa635</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Munasco Capital</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Single Family Office of the Munasco Group</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>https://www.munasco.com/</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Colombo</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="inlineStr"/>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr"/>
+      <c r="AJ209" t="inlineStr"/>
+      <c r="AK209" t="inlineStr"/>
+      <c r="AL209" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM209" t="inlineStr"/>
+      <c r="AN209" t="inlineStr"/>
+      <c r="AO209" t="inlineStr"/>
+      <c r="AP209" t="inlineStr"/>
+      <c r="AQ209" t="inlineStr"/>
+      <c r="AR209" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT209" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU209" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV209" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Tareem Enterprises for Investment</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single-family language</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Tareem Enterprises is a single-family investment office based in Riyadh, stewarding family capital across generations through patient, global investing.</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Tareem Enterprises is a private investment office that manages the wealth of a single family, deploying capital with patience and conviction into opportunities around the world.</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>https://tareement.com/</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>info@tareement.com</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
+      <c r="AE210" t="inlineStr"/>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr"/>
+      <c r="AJ210" t="inlineStr"/>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr"/>
+      <c r="AN210" t="inlineStr"/>
+      <c r="AO210" t="inlineStr"/>
+      <c r="AP210" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr"/>
+      <c r="AR210" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT210" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU210" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV210" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Matrix Capital</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Matrix Capital is a family office based in Riyadh, deploying Sharia-compliant capital across international real estate and strategic investments.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Matrix Capital is a family office based in Riyadh, deploying Sharia-compliant capital across international real estate and strategic investments.</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>https://matrixcapital.sa.com/</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>info@matrixcapital.sa.com</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
+      <c r="AE211" t="inlineStr"/>
+      <c r="AF211" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG211" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr"/>
+      <c r="AJ211" t="inlineStr"/>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL211" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM211" t="inlineStr"/>
+      <c r="AN211" t="inlineStr"/>
+      <c r="AO211" t="inlineStr"/>
+      <c r="AP211" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr"/>
+      <c r="AR211" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT211" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU211" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV211" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SMA Investment</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>SMA Investments</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Family offices in Saudi Arabia Headquartered in Riyadh, SMA Investment is a family office company that manages and oversees the investments and assets.</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>https://www.sma-investment.com/</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>YORK</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+      <c r="AE212" t="inlineStr"/>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr"/>
+      <c r="AI212" t="inlineStr"/>
+      <c r="AJ212" t="inlineStr"/>
+      <c r="AK212" t="inlineStr"/>
+      <c r="AL212" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr"/>
+      <c r="AN212" t="inlineStr"/>
+      <c r="AO212" t="inlineStr"/>
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr"/>
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT212" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU212" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV212" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>fo_2599b48b8b</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Najashi Holding</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Najashi Holding invests in healthcare biotech and life sciences in Saudi Arabia driving innovation partnerships and long term growth opportunities globally</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>We adopt a long-term investment approach supported by deep sector expertise, with a focus on driving growth and creating sustainable value.</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>https://najashiholding.com/</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
+      <c r="AE213" t="inlineStr"/>
+      <c r="AF213" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG213" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH213" t="inlineStr"/>
+      <c r="AI213" t="inlineStr"/>
+      <c r="AJ213" t="inlineStr"/>
+      <c r="AK213" t="inlineStr"/>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM213" t="inlineStr"/>
+      <c r="AN213" t="inlineStr"/>
+      <c r="AO213" t="inlineStr"/>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr"/>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT213" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV213" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>fo_f57a7a383e</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Efadha Alarabiya for Investments</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>The company's portfolio spans strategic allocation across multiple regions, blending strategic placements with opportunistic investment.</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>https://www.efadha.com/</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>info@efadha.com</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
+      <c r="AE214" t="inlineStr"/>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr"/>
+      <c r="AI214" t="inlineStr"/>
+      <c r="AJ214" t="inlineStr"/>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL214" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM214" t="inlineStr"/>
+      <c r="AN214" t="inlineStr"/>
+      <c r="AO214" t="inlineStr"/>
+      <c r="AP214" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr"/>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT214" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV214" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Baisan Family Office</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Single-Family Office</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single-family language</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Baisan Family Office</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Home | Baisan The Baisan Family Office is a private entity that manages the investments of the AlQahtani Family of Saudi Arabia.</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>https://www.baisan.co/</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Al Khobar</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>info@baisan.co</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr"/>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
+      <c r="AE215" t="inlineStr"/>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr"/>
+      <c r="AI215" t="inlineStr"/>
+      <c r="AJ215" t="inlineStr"/>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr"/>
+      <c r="AN215" t="inlineStr"/>
+      <c r="AO215" t="inlineStr"/>
+      <c r="AP215" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr"/>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT215" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV215" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>fo_786f44f9f4</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>SD Holding</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>SD Holding, Saudi family office (est. 2023), preserves legacy and fuels growth via value-aligned investments and community-driven CSR.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>We seek strategic investment opportunities that align with our values, fostering partnerships that drive long-term economic and social impact.</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>https://sdholding.sa/</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="inlineStr"/>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH216" t="inlineStr"/>
+      <c r="AI216" t="inlineStr"/>
+      <c r="AJ216" t="inlineStr"/>
+      <c r="AK216" t="inlineStr"/>
+      <c r="AL216" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM216" t="inlineStr"/>
+      <c r="AN216" t="inlineStr"/>
+      <c r="AO216" t="inlineStr"/>
+      <c r="AP216" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ216" t="inlineStr"/>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT216" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU216" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV216" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; firm_contact_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Al Nahdi Family Office</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SEC Form ADV / IAPD registration names it a family office; firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>The office works to preserve the family's values, history and wealth.</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>https://alnahdi-office.com/en</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>info@alnahdi-office.com</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
+      <c r="AE217" t="inlineStr"/>
+      <c r="AF217" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr"/>
+      <c r="AI217" t="inlineStr"/>
+      <c r="AJ217" t="inlineStr"/>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr"/>
+      <c r="AN217" t="inlineStr"/>
+      <c r="AO217" t="inlineStr"/>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr"/>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration) (firm registration, family-office status, type); Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT217" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Hajaj &amp; Associates</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>A family office that embodies the values of its diverse &amp; rooted members, birthing opportunities for generations to come.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>WHO WE ARE A cohesive family office that embodies the values of its diverse &amp; rooted members, birthing opportunities for generations to come.</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>https://www.hajaj.com/</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>info@hajaj.com</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
+      <c r="AE218" t="inlineStr"/>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr"/>
+      <c r="AI218" t="inlineStr"/>
+      <c r="AJ218" t="inlineStr"/>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL218" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr"/>
+      <c r="AN218" t="inlineStr"/>
+      <c r="AO218" t="inlineStr"/>
+      <c r="AP218" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr"/>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT218" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV218" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>fo_e6df4e865a</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Tawoos Group</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>firm website describes itself as a family office; type: single vs multi family not established</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>The Group is building its core strategic businesses while diversifying its investments into premium real estate development, global capital markets, private equity and venture capital.</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>https://www.tawoos.com/</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Muscat</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>info@tawoos.com</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>risky</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr"/>
+      <c r="X219" t="inlineStr"/>
+      <c r="Y219" t="inlineStr"/>
+      <c r="Z219" t="inlineStr"/>
+      <c r="AA219" t="inlineStr"/>
+      <c r="AB219" t="inlineStr"/>
+      <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr"/>
+      <c r="AE219" t="inlineStr"/>
+      <c r="AF219" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AG219" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AH219" t="inlineStr"/>
+      <c r="AI219" t="inlineStr"/>
+      <c r="AJ219" t="inlineStr"/>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AL219" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AM219" t="inlineStr"/>
+      <c r="AN219" t="inlineStr"/>
+      <c r="AO219" t="inlineStr"/>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr"/>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>Firm Website (family-office status, type)</t>
+        </is>
+      </c>
+      <c r="AT219" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AV219" t="inlineStr">
+        <is>
+          <t>corporate_linkedin; principal_linkedin; principal_email; principal_name; principal_title; principal_phone; estimated_aum</t>
+        </is>
+      </c>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>firm_contact_email is the firm's published contact inbox (official site) — a real, sourced channel but not a route to any named individual</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24215,7 +26506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H480"/>
+  <dimension ref="A1:H574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42461,6 +44752,3578 @@
         </is>
       </c>
       <c r="H480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>fo_e9e4e52a58</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>https://oppenheimer-daughters.com</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>fo_e9e4e52a58</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>https://oppenheimer-daughters.com/</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>fo_e9e4e52a58</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>https://oppenheimer-daughters.com/</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>fo_e9e4e52a58</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>https://tginvest.co.za</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>https://tginvest.co.za/</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>https://tginvest.co.za/</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>https://tginvest.co.za/</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>https://tginvest.co.za/</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>fo_f3583bbbe4</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>https://lucratus.co.za</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>fo_f3583bbbe4</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>https://lucratus.co.za/</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>fo_f3583bbbe4</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>https://lucratus.co.za/</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>fo_f3583bbbe4</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>https://lucratus.co.za/</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>fo_f3583bbbe4</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>https://baycapital.co.za</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/281675</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>https://baycapital.co.za/</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>https://baycapital.co.za/</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>https://baycapital.co.za/</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>https://baycapital.co.za/</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>estimated_aum</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/281675</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>principal_name</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/281675</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>principal_title</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>SEC Form ADV Part 1A (Item 5.F total AUM / Schedule A control person)</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/281675</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>https://gardecapital.co.za/wp</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/151043</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>https://gardecapital.co.za/wp/</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>https://gardecapital.co.za/wp/</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>https://gardecapital.co.za/wp/</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>https://gardecapital.co.za/wp/</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>https://www.sfo.co.za</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>https://www.sfo.co.za/</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>https://www.sfo.co.za/</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>https://www.sfo.co.za/</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>https://www.sfo.co.za/</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>fo_9cd2efa635</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>https://www.munasco.com</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>fo_9cd2efa635</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>https://www.munasco.com/</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>fo_9cd2efa635</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>https://www.munasco.com/</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>fo_9cd2efa635</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>https://tareement.com</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>https://tareement.com/</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>https://tareement.com/</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>https://tareement.com/</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>https://tareement.com/</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>https://matrixcapital.sa.com</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>https://matrixcapital.sa.com/</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>https://matrixcapital.sa.com/</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>https://matrixcapital.sa.com/</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>https://matrixcapital.sa.com/</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>https://www.sma-investment.com</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/121788</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>https://www.sma-investment.com/</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>https://www.sma-investment.com/</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>https://www.sma-investment.com/</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>fo_2599b48b8b</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>https://najashiholding.com</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>fo_2599b48b8b</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>https://najashiholding.com/</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>fo_2599b48b8b</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>https://najashiholding.com/</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>fo_2599b48b8b</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>https://najashiholding.com/</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>fo_2599b48b8b</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>fo_f57a7a383e</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>https://www.efadha.com</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>fo_f57a7a383e</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>https://www.efadha.com/</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>fo_f57a7a383e</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>https://www.efadha.com/</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>fo_f57a7a383e</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>https://www.efadha.com/</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>fo_f57a7a383e</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr"/>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>https://www.baisan.co</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>https://www.baisan.co/</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>https://www.baisan.co/</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>https://www.baisan.co/</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>https://www.baisan.co/</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr"/>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>fo_786f44f9f4</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>https://sdholding.sa</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>fo_786f44f9f4</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>https://sdholding.sa/</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>fo_786f44f9f4</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>https://sdholding.sa/</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>fo_786f44f9f4</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>https://sdholding.sa/</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>fo_786f44f9f4</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr"/>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>https://alnahdi-office.com/en</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>IAPD registration record</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/307144</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>https://alnahdi-office.com/en</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>https://alnahdi-office.com/en</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>https://alnahdi-office.com/en</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>https://www.hajaj.com</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>https://www.hajaj.com/</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>website meta description</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>https://www.hajaj.com/</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>https://www.hajaj.com/</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>https://www.hajaj.com/</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr"/>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>fo_e6df4e865a</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>firm website</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>https://www.tawoos.com</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>fo_e6df4e865a</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>fetched firm website</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>https://www.tawoos.com/</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>fo_e6df4e865a</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>investment_thesis</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>firm website (stated investment approach / mission)</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>https://www.tawoos.com/</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>fo_e6df4e865a</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>firm_contact_email</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>firm website (published contact / mailto link)</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>https://www.tawoos.com/</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>fo_e6df4e865a</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>hq_country</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>discovery-source filing/record address</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>location from the discovery source (e.g. IRS 990-PF / directory)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -42473,7 +48336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F509"/>
+  <dimension ref="A1:F549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56567,6 +62430,1150 @@
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>fo_e9e4e52a58</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>https://oppenheimer-daughters.com/</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>fo_e9e4e52a58</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
+      <c r="E511" t="inlineStr"/>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>https://tginvest.co.za/</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>fo_1a373a1f46</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>fo_f3583bbbe4</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>https://lucratus.co.za/</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>fo_f3583bbbe4</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr"/>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/281675</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>https://baycapital.co.za/</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>total regulatory AUM (ADV Item 5.F), owner/control person (ADV Schedule A)</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/281675</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>fo_5278beed8e</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/151043</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>https://gardecapital.co.za/wp/</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>fo_60304a2052</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr"/>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>https://www.sfo.co.za/</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>fo_f40f8874d6</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr"/>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>fo_9cd2efa635</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>https://www.munasco.com/</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>fo_9cd2efa635</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr"/>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>https://tareement.com/</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>fo_9d0d8d7af2</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/11544</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>https://matrixcapital.sa.com/</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>fo_7438841ecd</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr"/>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/121788</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>https://www.sma-investment.com/</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>fo_0fbfd13b10</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>fo_2599b48b8b</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>https://najashiholding.com/</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>fo_2599b48b8b</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>fo_f57a7a383e</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>https://www.efadha.com/</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>fo_f57a7a383e</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr"/>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>https://www.baisan.co/</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>fo_1e6c828eaa</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>fo_786f44f9f4</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>https://sdholding.sa/</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>fo_786f44f9f4</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr"/>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>SEC IAPD / Form ADV (investment-adviser registration)</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>firm registration, family-office status, type</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>https://adviserinfo.sec.gov/firm/summary/307144</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>https://alnahdi-office.com/en</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>fo_7c3fe4244a</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>https://www.hajaj.com/</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>fo_f91455fc53</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" t="inlineStr"/>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>fo_e6df4e865a</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>verification</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Firm Website</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>family-office status, type</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>https://www.tawoos.com/</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>fo_e6df4e865a</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>discovery</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
